--- a/Data/Protein/Price_Pig.xlsx
+++ b/Data/Protein/Price_Pig.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6318875413f076c7/Escritorio/Work/Master Thesis/Laks/Data/Protein/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s2310053\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{4880D93A-C823-45CA-9F74-BF5E8A13FDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{481642C4-2FDC-4ABF-B51C-021038507590}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06245F62-8058-4D22-BD14-E58AA38FE8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{82E07D71-83BB-485F-B47B-DF280419A61D}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{EA5F6D04-2CD1-49B2-8BF8-AC6006E47C2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -48,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,14 +416,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24536314-78E6-414E-BEB9-21BE33CE1C51}">
-  <dimension ref="A1:B644"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2F2463-D442-4BC5-ABCE-3B8F74307126}">
+  <dimension ref="A1:B648"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -428,5147 +431,5179 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2">
       <c r="A2" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B2">
+        <v>1812.58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B3">
+        <v>1832.21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B4">
+        <v>1875.45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B5">
+        <v>1951.95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1">
         <v>46136</v>
       </c>
-      <c r="B2">
+      <c r="B6">
         <v>1953.69</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="1">
+    <row r="7" spans="1:2">
+      <c r="A7" s="1">
         <v>46129</v>
       </c>
-      <c r="B3">
+      <c r="B7">
         <v>1968.53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="1">
+    <row r="8" spans="1:2">
+      <c r="A8" s="1">
         <v>46122</v>
       </c>
-      <c r="B4">
+      <c r="B8">
         <v>1993.04</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="1">
+    <row r="9" spans="1:2">
+      <c r="A9" s="1">
         <v>46115</v>
       </c>
-      <c r="B5">
+      <c r="B9">
         <v>2009.01</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" s="1">
+    <row r="10" spans="1:2">
+      <c r="A10" s="1">
         <v>46108</v>
       </c>
-      <c r="B6">
+      <c r="B10">
         <v>2003.3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="1">
+    <row r="11" spans="1:2">
+      <c r="A11" s="1">
         <v>46101</v>
       </c>
-      <c r="B7">
+      <c r="B11">
         <v>1970.8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" s="1">
+    <row r="12" spans="1:2">
+      <c r="A12" s="1">
         <v>46094</v>
       </c>
-      <c r="B8">
+      <c r="B12">
         <v>1956.35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="1">
+    <row r="13" spans="1:2">
+      <c r="A13" s="1">
         <v>46087</v>
       </c>
-      <c r="B9">
+      <c r="B13">
         <v>1860.7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="1">
+    <row r="14" spans="1:2">
+      <c r="A14" s="1">
         <v>46080</v>
       </c>
-      <c r="B10">
+      <c r="B14">
         <v>1826.45</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="1">
+    <row r="15" spans="1:2">
+      <c r="A15" s="1">
         <v>46073</v>
       </c>
-      <c r="B11">
+      <c r="B15">
         <v>1770.15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" s="1">
+    <row r="16" spans="1:2">
+      <c r="A16" s="1">
         <v>46066</v>
       </c>
-      <c r="B12">
+      <c r="B16">
         <v>1739.91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" s="1">
+    <row r="17" spans="1:2">
+      <c r="A17" s="1">
         <v>46059</v>
       </c>
-      <c r="B13">
+      <c r="B17">
         <v>1758.52</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" s="1">
+    <row r="18" spans="1:2">
+      <c r="A18" s="1">
         <v>46052</v>
       </c>
-      <c r="B14">
+      <c r="B18">
         <v>1764.23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" s="1">
+    <row r="19" spans="1:2">
+      <c r="A19" s="1">
         <v>46045</v>
       </c>
-      <c r="B15">
+      <c r="B19">
         <v>1784.98</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" s="1">
+    <row r="20" spans="1:2">
+      <c r="A20" s="1">
         <v>46038</v>
       </c>
-      <c r="B16">
+      <c r="B20">
         <v>1815.95</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="1">
+    <row r="21" spans="1:2">
+      <c r="A21" s="1">
         <v>46031</v>
       </c>
-      <c r="B17">
+      <c r="B21">
         <v>1883.04</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="1">
+    <row r="22" spans="1:2">
+      <c r="A22" s="1">
         <v>46024</v>
       </c>
-      <c r="B18">
+      <c r="B22">
         <v>1990.87</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" s="1">
+    <row r="23" spans="1:2">
+      <c r="A23" s="1">
         <v>46017</v>
       </c>
-      <c r="B19">
+      <c r="B23">
         <v>2027.47</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="1">
+    <row r="24" spans="1:2">
+      <c r="A24" s="1">
         <v>46010</v>
       </c>
-      <c r="B20">
+      <c r="B24">
         <v>2019.43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" s="1">
+    <row r="25" spans="1:2">
+      <c r="A25" s="1">
         <v>46003</v>
       </c>
-      <c r="B21">
+      <c r="B25">
         <v>2021.85</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" s="1">
+    <row r="26" spans="1:2">
+      <c r="A26" s="1">
         <v>45996</v>
       </c>
-      <c r="B22">
+      <c r="B26">
         <v>2002.09</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="1">
+    <row r="27" spans="1:2">
+      <c r="A27" s="1">
         <v>45989</v>
       </c>
-      <c r="B23">
+      <c r="B27">
         <v>2000.95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="1">
+    <row r="28" spans="1:2">
+      <c r="A28" s="1">
         <v>45982</v>
       </c>
-      <c r="B24">
+      <c r="B28">
         <v>2051.3200000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="1">
+    <row r="29" spans="1:2">
+      <c r="A29" s="1">
         <v>45975</v>
       </c>
-      <c r="B25">
+      <c r="B29">
         <v>2107.4699999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="1">
+    <row r="30" spans="1:2">
+      <c r="A30" s="1">
         <v>45968</v>
       </c>
-      <c r="B26">
+      <c r="B30">
         <v>2112.73</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="1">
+    <row r="31" spans="1:2">
+      <c r="A31" s="1">
         <v>45961</v>
       </c>
-      <c r="B27">
+      <c r="B31">
         <v>2105.64</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" s="1">
+    <row r="32" spans="1:2">
+      <c r="A32" s="1">
         <v>45954</v>
       </c>
-      <c r="B28">
+      <c r="B32">
         <v>2095.5300000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="1">
+    <row r="33" spans="1:2">
+      <c r="A33" s="1">
         <v>45947</v>
       </c>
-      <c r="B29">
+      <c r="B33">
         <v>2124.02</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" s="1">
+    <row r="34" spans="1:2">
+      <c r="A34" s="1">
         <v>45940</v>
       </c>
-      <c r="B30">
+      <c r="B34">
         <v>2191.08</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" s="1">
+    <row r="35" spans="1:2">
+      <c r="A35" s="1">
         <v>45933</v>
       </c>
-      <c r="B31">
+      <c r="B35">
         <v>2277.23</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" s="1">
+    <row r="36" spans="1:2">
+      <c r="A36" s="1">
         <v>45926</v>
       </c>
-      <c r="B32">
+      <c r="B36">
         <v>2278.69</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" s="1">
+    <row r="37" spans="1:2">
+      <c r="A37" s="1">
         <v>45919</v>
       </c>
-      <c r="B33">
+      <c r="B37">
         <v>2327.1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" s="1">
+    <row r="38" spans="1:2">
+      <c r="A38" s="1">
         <v>45912</v>
       </c>
-      <c r="B34">
+      <c r="B38">
         <v>2368.31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" s="1">
+    <row r="39" spans="1:2">
+      <c r="A39" s="1">
         <v>45905</v>
       </c>
-      <c r="B35">
+      <c r="B39">
         <v>2414.25</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" s="1">
+    <row r="40" spans="1:2">
+      <c r="A40" s="1">
         <v>45898</v>
       </c>
-      <c r="B36">
+      <c r="B40">
         <v>2411.5300000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" s="1">
+    <row r="41" spans="1:2">
+      <c r="A41" s="1">
         <v>45891</v>
       </c>
-      <c r="B37">
+      <c r="B41">
         <v>2410.8200000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" s="1">
+    <row r="42" spans="1:2">
+      <c r="A42" s="1">
         <v>45884</v>
       </c>
-      <c r="B38">
+      <c r="B42">
         <v>2439.3000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" s="1">
+    <row r="43" spans="1:2">
+      <c r="A43" s="1">
         <v>45877</v>
       </c>
-      <c r="B39">
+      <c r="B43">
         <v>2455.09</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" s="1">
+    <row r="44" spans="1:2">
+      <c r="A44" s="1">
         <v>45870</v>
       </c>
-      <c r="B40">
+      <c r="B44">
         <v>2426.6799999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" s="1">
+    <row r="45" spans="1:2">
+      <c r="A45" s="1">
         <v>45863</v>
       </c>
-      <c r="B41">
+      <c r="B45">
         <v>2445.75</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" s="1">
+    <row r="46" spans="1:2">
+      <c r="A46" s="1">
         <v>45856</v>
       </c>
-      <c r="B42">
+      <c r="B46">
         <v>2419.25</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" s="1">
+    <row r="47" spans="1:2">
+      <c r="A47" s="1">
         <v>45849</v>
       </c>
-      <c r="B43">
+      <c r="B47">
         <v>2427.56</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" s="1">
+    <row r="48" spans="1:2">
+      <c r="A48" s="1">
         <v>45842</v>
       </c>
-      <c r="B44">
+      <c r="B48">
         <v>2492.8200000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" s="1">
+    <row r="49" spans="1:2">
+      <c r="A49" s="1">
         <v>45835</v>
       </c>
-      <c r="B45">
+      <c r="B49">
         <v>2589.7399999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="1">
+    <row r="50" spans="1:2">
+      <c r="A50" s="1">
         <v>45828</v>
       </c>
-      <c r="B46">
+      <c r="B50">
         <v>2557.38</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47" s="1">
+    <row r="51" spans="1:2">
+      <c r="A51" s="1">
         <v>45821</v>
       </c>
-      <c r="B47">
+      <c r="B51">
         <v>2506.16</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" s="1">
+    <row r="52" spans="1:2">
+      <c r="A52" s="1">
         <v>45814</v>
       </c>
-      <c r="B48">
+      <c r="B52">
         <v>2526.2399999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" s="1">
+    <row r="53" spans="1:2">
+      <c r="A53" s="1">
         <v>45807</v>
       </c>
-      <c r="B49">
+      <c r="B53">
         <v>2537.25</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A50" s="1">
+    <row r="54" spans="1:2">
+      <c r="A54" s="1">
         <v>45800</v>
       </c>
-      <c r="B50">
+      <c r="B54">
         <v>2465.15</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A51" s="1">
+    <row r="55" spans="1:2">
+      <c r="A55" s="1">
         <v>45793</v>
       </c>
-      <c r="B51">
+      <c r="B55">
         <v>2428.1999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52" s="1">
+    <row r="56" spans="1:2">
+      <c r="A56" s="1">
         <v>45786</v>
       </c>
-      <c r="B52">
+      <c r="B56">
         <v>2433.46</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A53" s="1">
+    <row r="57" spans="1:2">
+      <c r="A57" s="1">
         <v>45779</v>
       </c>
-      <c r="B53">
+      <c r="B57">
         <v>2464.08</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54" s="1">
+    <row r="58" spans="1:2">
+      <c r="A58" s="1">
         <v>45772</v>
       </c>
-      <c r="B54">
+      <c r="B58">
         <v>2459.85</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A55" s="1">
+    <row r="59" spans="1:2">
+      <c r="A59" s="1">
         <v>45765</v>
       </c>
-      <c r="B55">
+      <c r="B59">
         <v>2437.62</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A56" s="1">
+    <row r="60" spans="1:2">
+      <c r="A60" s="1">
         <v>45758</v>
       </c>
-      <c r="B56">
+      <c r="B60">
         <v>2454.41</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A57" s="1">
+    <row r="61" spans="1:2">
+      <c r="A61" s="1">
         <v>45751</v>
       </c>
-      <c r="B57">
+      <c r="B61">
         <v>2359.5500000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A58" s="1">
+    <row r="62" spans="1:2">
+      <c r="A62" s="1">
         <v>45744</v>
       </c>
-      <c r="B58">
+      <c r="B62">
         <v>2135.52</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A59" s="1">
+    <row r="63" spans="1:2">
+      <c r="A63" s="1">
         <v>45737</v>
       </c>
-      <c r="B59">
+      <c r="B63">
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A60" s="1">
+    <row r="64" spans="1:2">
+      <c r="A64" s="1">
         <v>45730</v>
       </c>
-      <c r="B60">
+      <c r="B64">
         <v>2081.8200000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A61" s="1">
+    <row r="65" spans="1:2">
+      <c r="A65" s="1">
         <v>45723</v>
       </c>
-      <c r="B61">
+      <c r="B65">
         <v>2112.59</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A62" s="1">
+    <row r="66" spans="1:2">
+      <c r="A66" s="1">
         <v>45716</v>
       </c>
-      <c r="B62">
+      <c r="B66">
         <v>2104.0100000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A63" s="1">
+    <row r="67" spans="1:2">
+      <c r="A67" s="1">
         <v>45709</v>
       </c>
-      <c r="B63">
+      <c r="B67">
         <v>2095.27</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A64" s="1">
+    <row r="68" spans="1:2">
+      <c r="A68" s="1">
         <v>45702</v>
       </c>
-      <c r="B64">
+      <c r="B68">
         <v>2105.5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A65" s="1">
+    <row r="69" spans="1:2">
+      <c r="A69" s="1">
         <v>45695</v>
       </c>
-      <c r="B65">
+      <c r="B69">
         <v>2096.39</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A66" s="1">
+    <row r="70" spans="1:2">
+      <c r="A70" s="1">
         <v>45688</v>
       </c>
-      <c r="B66">
+      <c r="B70">
         <v>2133.88</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A67" s="1">
+    <row r="71" spans="1:2">
+      <c r="A71" s="1">
         <v>45681</v>
       </c>
-      <c r="B67">
+      <c r="B71">
         <v>2136.3000000000002</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A68" s="1">
+    <row r="72" spans="1:2">
+      <c r="A72" s="1">
         <v>45674</v>
       </c>
-      <c r="B68">
+      <c r="B72">
         <v>2191.2600000000002</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A69" s="1">
+    <row r="73" spans="1:2">
+      <c r="A73" s="1">
         <v>45667</v>
       </c>
-      <c r="B69">
+      <c r="B73">
         <v>2295.4899999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A70" s="1">
+    <row r="74" spans="1:2">
+      <c r="A74" s="1">
         <v>45660</v>
       </c>
-      <c r="B70">
+      <c r="B74">
         <v>2361.14</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A71" s="1">
+    <row r="75" spans="1:2">
+      <c r="A75" s="1">
         <v>45653</v>
       </c>
-      <c r="B71">
+      <c r="B75">
         <v>2398.5700000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A72" s="1">
+    <row r="76" spans="1:2">
+      <c r="A76" s="1">
         <v>45646</v>
       </c>
-      <c r="B72">
+      <c r="B76">
         <v>2391.15</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A73" s="1">
+    <row r="77" spans="1:2">
+      <c r="A77" s="1">
         <v>45639</v>
       </c>
-      <c r="B73">
+      <c r="B77">
         <v>2364.34</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A74" s="1">
+    <row r="78" spans="1:2">
+      <c r="A78" s="1">
         <v>45632</v>
       </c>
-      <c r="B74">
+      <c r="B78">
         <v>2377.34</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A75" s="1">
+    <row r="79" spans="1:2">
+      <c r="A79" s="1">
         <v>45625</v>
       </c>
-      <c r="B75">
+      <c r="B79">
         <v>2357.83</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A76" s="1">
+    <row r="80" spans="1:2">
+      <c r="A80" s="1">
         <v>45618</v>
       </c>
-      <c r="B76">
+      <c r="B80">
         <v>2328.91</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A77" s="1">
+    <row r="81" spans="1:2">
+      <c r="A81" s="1">
         <v>45611</v>
       </c>
-      <c r="B77">
+      <c r="B81">
         <v>2359.0100000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A78" s="1">
+    <row r="82" spans="1:2">
+      <c r="A82" s="1">
         <v>45604</v>
       </c>
-      <c r="B78">
+      <c r="B82">
         <v>2385.2800000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A79" s="1">
+    <row r="83" spans="1:2">
+      <c r="A83" s="1">
         <v>45597</v>
       </c>
-      <c r="B79">
+      <c r="B83">
         <v>2426.77</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A80" s="1">
+    <row r="84" spans="1:2">
+      <c r="A84" s="1">
         <v>45590</v>
       </c>
-      <c r="B80">
+      <c r="B84">
         <v>2427.71</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A81" s="1">
+    <row r="85" spans="1:2">
+      <c r="A85" s="1">
         <v>45583</v>
       </c>
-      <c r="B81">
+      <c r="B85">
         <v>2491.0300000000002</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A82" s="1">
+    <row r="86" spans="1:2">
+      <c r="A86" s="1">
         <v>45576</v>
       </c>
-      <c r="B82">
+      <c r="B86">
         <v>2449.48</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A83" s="1">
+    <row r="87" spans="1:2">
+      <c r="A87" s="1">
         <v>45569</v>
       </c>
-      <c r="B83">
+      <c r="B87">
         <v>2457.6</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A84" s="1">
+    <row r="88" spans="1:2">
+      <c r="A88" s="1">
         <v>45562</v>
       </c>
-      <c r="B84">
+      <c r="B88">
         <v>2467.8000000000002</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A85" s="1">
+    <row r="89" spans="1:2">
+      <c r="A89" s="1">
         <v>45555</v>
       </c>
-      <c r="B85">
+      <c r="B89">
         <v>2458.61</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A86" s="1">
+    <row r="90" spans="1:2">
+      <c r="A90" s="1">
         <v>45548</v>
       </c>
-      <c r="B86">
+      <c r="B90">
         <v>2483.71</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A87" s="1">
+    <row r="91" spans="1:2">
+      <c r="A91" s="1">
         <v>45541</v>
       </c>
-      <c r="B87">
+      <c r="B91">
         <v>2496.46</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A88" s="1">
+    <row r="92" spans="1:2">
+      <c r="A92" s="1">
         <v>45534</v>
       </c>
-      <c r="B88">
+      <c r="B92">
         <v>2468.11</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A89" s="1">
+    <row r="93" spans="1:2">
+      <c r="A93" s="1">
         <v>45527</v>
       </c>
-      <c r="B89">
+      <c r="B93">
         <v>2463.1799999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A90" s="1">
+    <row r="94" spans="1:2">
+      <c r="A94" s="1">
         <v>45520</v>
       </c>
-      <c r="B90">
+      <c r="B94">
         <v>2485.83</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A91" s="1">
+    <row r="95" spans="1:2">
+      <c r="A95" s="1">
         <v>45513</v>
       </c>
-      <c r="B91">
+      <c r="B95">
         <v>2529.3000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A92" s="1">
+    <row r="96" spans="1:2">
+      <c r="A96" s="1">
         <v>45506</v>
       </c>
-      <c r="B92">
+      <c r="B96">
         <v>2634.95</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A93" s="1">
+    <row r="97" spans="1:2">
+      <c r="A97" s="1">
         <v>45499</v>
       </c>
-      <c r="B93">
+      <c r="B97">
         <v>2640.97</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A94" s="1">
+    <row r="98" spans="1:2">
+      <c r="A98" s="1">
         <v>45492</v>
       </c>
-      <c r="B94">
+      <c r="B98">
         <v>2619.9499999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A95" s="1">
+    <row r="99" spans="1:2">
+      <c r="A99" s="1">
         <v>45485</v>
       </c>
-      <c r="B95">
+      <c r="B99">
         <v>2585.98</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A96" s="1">
+    <row r="100" spans="1:2">
+      <c r="A100" s="1">
         <v>45478</v>
       </c>
-      <c r="B96">
+      <c r="B100">
         <v>2564.85</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A97" s="1">
+    <row r="101" spans="1:2">
+      <c r="A101" s="1">
         <v>45471</v>
       </c>
-      <c r="B97">
+      <c r="B101">
         <v>2637.83</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A98" s="1">
+    <row r="102" spans="1:2">
+      <c r="A102" s="1">
         <v>45464</v>
       </c>
-      <c r="B98">
+      <c r="B102">
         <v>2609.7800000000002</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A99" s="1">
+    <row r="103" spans="1:2">
+      <c r="A103" s="1">
         <v>45457</v>
       </c>
-      <c r="B99">
+      <c r="B103">
         <v>2636.26</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A100" s="1">
+    <row r="104" spans="1:2">
+      <c r="A104" s="1">
         <v>45450</v>
       </c>
-      <c r="B100">
+      <c r="B104">
         <v>2675.04</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A101" s="1">
+    <row r="105" spans="1:2">
+      <c r="A105" s="1">
         <v>45443</v>
       </c>
-      <c r="B101">
+      <c r="B105">
         <v>2633.11</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A102" s="1">
+    <row r="106" spans="1:2">
+      <c r="A106" s="1">
         <v>45436</v>
       </c>
-      <c r="B102">
+      <c r="B106">
         <v>2655.12</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A103" s="1">
+    <row r="107" spans="1:2">
+      <c r="A107" s="1">
         <v>45429</v>
       </c>
-      <c r="B103">
+      <c r="B107">
         <v>2684.6</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A104" s="1">
+    <row r="108" spans="1:2">
+      <c r="A108" s="1">
         <v>45422</v>
       </c>
-      <c r="B104">
+      <c r="B108">
         <v>2702.53</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A105" s="1">
+    <row r="109" spans="1:2">
+      <c r="A109" s="1">
         <v>45415</v>
       </c>
-      <c r="B105">
+      <c r="B109">
         <v>2699.01</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A106" s="1">
+    <row r="110" spans="1:2">
+      <c r="A110" s="1">
         <v>45408</v>
       </c>
-      <c r="B106">
+      <c r="B110">
         <v>2718.48</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A107" s="1">
+    <row r="111" spans="1:2">
+      <c r="A111" s="1">
         <v>45401</v>
       </c>
-      <c r="B107">
+      <c r="B111">
         <v>2708.01</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A108" s="1">
+    <row r="112" spans="1:2">
+      <c r="A112" s="1">
         <v>45394</v>
       </c>
-      <c r="B108">
+      <c r="B112">
         <v>2679.5</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A109" s="1">
+    <row r="113" spans="1:2">
+      <c r="A113" s="1">
         <v>45387</v>
       </c>
-      <c r="B109">
+      <c r="B113">
         <v>2683.4</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A110" s="1">
+    <row r="114" spans="1:2">
+      <c r="A114" s="1">
         <v>45380</v>
       </c>
-      <c r="B110">
+      <c r="B114">
         <v>2697.74</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A111" s="1">
+    <row r="115" spans="1:2">
+      <c r="A115" s="1">
         <v>45373</v>
       </c>
-      <c r="B111">
+      <c r="B115">
         <v>2681.5</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A112" s="1">
+    <row r="116" spans="1:2">
+      <c r="A116" s="1">
         <v>45366</v>
       </c>
-      <c r="B112">
+      <c r="B116">
         <v>2673.58</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A113" s="1">
+    <row r="117" spans="1:2">
+      <c r="A117" s="1">
         <v>45359</v>
       </c>
-      <c r="B113">
+      <c r="B117">
         <v>2632.09</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A114" s="1">
+    <row r="118" spans="1:2">
+      <c r="A118" s="1">
         <v>45352</v>
       </c>
-      <c r="B114">
+      <c r="B118">
         <v>2614.17</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A115" s="1">
+    <row r="119" spans="1:2">
+      <c r="A119" s="1">
         <v>45345</v>
       </c>
-      <c r="B115">
+      <c r="B119">
         <v>2573.33</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A116" s="1">
+    <row r="120" spans="1:2">
+      <c r="A120" s="1">
         <v>45338</v>
       </c>
-      <c r="B116">
+      <c r="B120">
         <v>2534.92</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A117" s="1">
+    <row r="121" spans="1:2">
+      <c r="A121" s="1">
         <v>45331</v>
       </c>
-      <c r="B117">
+      <c r="B121">
         <v>2471.46</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A118" s="1">
+    <row r="122" spans="1:2">
+      <c r="A122" s="1">
         <v>45324</v>
       </c>
-      <c r="B118">
+      <c r="B122">
         <v>2413.2199999999998</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A119" s="1">
+    <row r="123" spans="1:2">
+      <c r="A123" s="1">
         <v>45317</v>
       </c>
-      <c r="B119">
+      <c r="B123">
         <v>2382.81</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A120" s="1">
+    <row r="124" spans="1:2">
+      <c r="A124" s="1">
         <v>45310</v>
       </c>
-      <c r="B120">
+      <c r="B124">
         <v>2445.0300000000002</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A121" s="1">
+    <row r="125" spans="1:2">
+      <c r="A125" s="1">
         <v>45303</v>
       </c>
-      <c r="B121">
+      <c r="B125">
         <v>2488.75</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A122" s="1">
+    <row r="126" spans="1:2">
+      <c r="A126" s="1">
         <v>45296</v>
       </c>
-      <c r="B122">
+      <c r="B126">
         <v>2484.86</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A123" s="1">
+    <row r="127" spans="1:2">
+      <c r="A127" s="1">
         <v>45289</v>
       </c>
-      <c r="B123">
+      <c r="B127">
         <v>2467.65</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A124" s="1">
+    <row r="128" spans="1:2">
+      <c r="A128" s="1">
         <v>45282</v>
       </c>
-      <c r="B124">
+      <c r="B128">
         <v>2484.85</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A125" s="1">
+    <row r="129" spans="1:2">
+      <c r="A129" s="1">
         <v>45275</v>
       </c>
-      <c r="B125">
+      <c r="B129">
         <v>2514.11</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A126" s="1">
+    <row r="130" spans="1:2">
+      <c r="A130" s="1">
         <v>45268</v>
       </c>
-      <c r="B126">
+      <c r="B130">
         <v>2588.29</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A127" s="1">
+    <row r="131" spans="1:2">
+      <c r="A131" s="1">
         <v>45261</v>
       </c>
-      <c r="B127">
+      <c r="B131">
         <v>2554.77</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A128" s="1">
+    <row r="132" spans="1:2">
+      <c r="A132" s="1">
         <v>45254</v>
       </c>
-      <c r="B128">
+      <c r="B132">
         <v>2572.34</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A129" s="1">
+    <row r="133" spans="1:2">
+      <c r="A133" s="1">
         <v>45247</v>
       </c>
-      <c r="B129">
+      <c r="B133">
         <v>2597.81</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A130" s="1">
+    <row r="134" spans="1:2">
+      <c r="A134" s="1">
         <v>45240</v>
       </c>
-      <c r="B130">
+      <c r="B134">
         <v>2619.1799999999998</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A131" s="1">
+    <row r="135" spans="1:2">
+      <c r="A135" s="1">
         <v>45233</v>
       </c>
-      <c r="B131">
+      <c r="B135">
         <v>2610.79</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A132" s="1">
+    <row r="136" spans="1:2">
+      <c r="A136" s="1">
         <v>45226</v>
       </c>
-      <c r="B132">
+      <c r="B136">
         <v>2606.31</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A133" s="1">
+    <row r="137" spans="1:2">
+      <c r="A137" s="1">
         <v>45219</v>
       </c>
-      <c r="B133">
+      <c r="B137">
         <v>2582.41</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A134" s="1">
+    <row r="138" spans="1:2">
+      <c r="A138" s="1">
         <v>45212</v>
       </c>
-      <c r="B134">
+      <c r="B138">
         <v>2584.0700000000002</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A135" s="1">
+    <row r="139" spans="1:2">
+      <c r="A139" s="1">
         <v>45205</v>
       </c>
-      <c r="B135">
+      <c r="B139">
         <v>2686.96</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A136" s="1">
+    <row r="140" spans="1:2">
+      <c r="A140" s="1">
         <v>45198</v>
       </c>
-      <c r="B136">
+      <c r="B140">
         <v>2655.77</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A137" s="1">
+    <row r="141" spans="1:2">
+      <c r="A141" s="1">
         <v>45191</v>
       </c>
-      <c r="B137">
+      <c r="B141">
         <v>2722.76</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A138" s="1">
+    <row r="142" spans="1:2">
+      <c r="A142" s="1">
         <v>45184</v>
       </c>
-      <c r="B138">
+      <c r="B142">
         <v>2764.53</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A139" s="1">
+    <row r="143" spans="1:2">
+      <c r="A143" s="1">
         <v>45177</v>
       </c>
-      <c r="B139">
+      <c r="B143">
         <v>2749</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A140" s="1">
+    <row r="144" spans="1:2">
+      <c r="A144" s="1">
         <v>45170</v>
       </c>
-      <c r="B140">
+      <c r="B144">
         <v>2770.51</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A141" s="1">
+    <row r="145" spans="1:2">
+      <c r="A145" s="1">
         <v>45163</v>
       </c>
-      <c r="B141">
+      <c r="B145">
         <v>2791.52</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A142" s="1">
+    <row r="146" spans="1:2">
+      <c r="A146" s="1">
         <v>45156</v>
       </c>
-      <c r="B142">
+      <c r="B146">
         <v>2832.97</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A143" s="1">
+    <row r="147" spans="1:2">
+      <c r="A147" s="1">
         <v>45149</v>
       </c>
-      <c r="B143">
+      <c r="B147">
         <v>2864.91</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A144" s="1">
+    <row r="148" spans="1:2">
+      <c r="A148" s="1">
         <v>45142</v>
       </c>
-      <c r="B144">
+      <c r="B148">
         <v>2837.63</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A145" s="1">
+    <row r="149" spans="1:2">
+      <c r="A149" s="1">
         <v>45135</v>
       </c>
-      <c r="B145">
+      <c r="B149">
         <v>2925.77</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A146" s="1">
+    <row r="150" spans="1:2">
+      <c r="A150" s="1">
         <v>45128</v>
       </c>
-      <c r="B146">
+      <c r="B150">
         <v>2925.45</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A147" s="1">
+    <row r="151" spans="1:2">
+      <c r="A151" s="1">
         <v>45121</v>
       </c>
-      <c r="B147">
+      <c r="B151">
         <v>2936.49</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A148" s="1">
+    <row r="152" spans="1:2">
+      <c r="A152" s="1">
         <v>45114</v>
       </c>
-      <c r="B148">
+      <c r="B152">
         <v>3022.33</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A149" s="1">
+    <row r="153" spans="1:2">
+      <c r="A153" s="1">
         <v>45107</v>
       </c>
-      <c r="B149">
+      <c r="B153">
         <v>3009.23</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A150" s="1">
+    <row r="154" spans="1:2">
+      <c r="A154" s="1">
         <v>45100</v>
       </c>
-      <c r="B150">
+      <c r="B154">
         <v>2996.78</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A151" s="1">
+    <row r="155" spans="1:2">
+      <c r="A155" s="1">
         <v>45093</v>
       </c>
-      <c r="B151">
+      <c r="B155">
         <v>2934.37</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A152" s="1">
+    <row r="156" spans="1:2">
+      <c r="A156" s="1">
         <v>45086</v>
       </c>
-      <c r="B152">
+      <c r="B156">
         <v>2905.44</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A153" s="1">
+    <row r="157" spans="1:2">
+      <c r="A157" s="1">
         <v>45079</v>
       </c>
-      <c r="B153">
+      <c r="B157">
         <v>2926.76</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A154" s="1">
+    <row r="158" spans="1:2">
+      <c r="A158" s="1">
         <v>45072</v>
       </c>
-      <c r="B154">
+      <c r="B158">
         <v>2929.08</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A155" s="1">
+    <row r="159" spans="1:2">
+      <c r="A159" s="1">
         <v>45065</v>
       </c>
-      <c r="B155">
+      <c r="B159">
         <v>2857.4</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A156" s="1">
+    <row r="160" spans="1:2">
+      <c r="A160" s="1">
         <v>45058</v>
       </c>
-      <c r="B156">
+      <c r="B160">
         <v>2818.02</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A157" s="1">
+    <row r="161" spans="1:2">
+      <c r="A161" s="1">
         <v>45051</v>
       </c>
-      <c r="B157">
+      <c r="B161">
         <v>2838.64</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A158" s="1">
+    <row r="162" spans="1:2">
+      <c r="A162" s="1">
         <v>45044</v>
       </c>
-      <c r="B158">
+      <c r="B162">
         <v>2857.02</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A159" s="1">
+    <row r="163" spans="1:2">
+      <c r="A163" s="1">
         <v>45037</v>
       </c>
-      <c r="B159">
+      <c r="B163">
         <v>2826.22</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A160" s="1">
+    <row r="164" spans="1:2">
+      <c r="A164" s="1">
         <v>45030</v>
       </c>
-      <c r="B160">
+      <c r="B164">
         <v>2777.52</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A161" s="1">
+    <row r="165" spans="1:2">
+      <c r="A165" s="1">
         <v>45023</v>
       </c>
-      <c r="B161">
+      <c r="B165">
         <v>2783.02</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A162" s="1">
+    <row r="166" spans="1:2">
+      <c r="A166" s="1">
         <v>45016</v>
       </c>
-      <c r="B162">
+      <c r="B166">
         <v>2758.52</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A163" s="1">
+    <row r="167" spans="1:2">
+      <c r="A167" s="1">
         <v>45009</v>
       </c>
-      <c r="B163">
+      <c r="B167">
         <v>2720.31</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A164" s="1">
+    <row r="168" spans="1:2">
+      <c r="A168" s="1">
         <v>45002</v>
       </c>
-      <c r="B164">
+      <c r="B168">
         <v>2712.19</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A165" s="1">
+    <row r="169" spans="1:2">
+      <c r="A169" s="1">
         <v>44995</v>
       </c>
-      <c r="B165">
+      <c r="B169">
         <v>2684.09</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A166" s="1">
+    <row r="170" spans="1:2">
+      <c r="A170" s="1">
         <v>44988</v>
       </c>
-      <c r="B166">
+      <c r="B170">
         <v>2618.85</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A167" s="1">
+    <row r="171" spans="1:2">
+      <c r="A171" s="1">
         <v>44981</v>
       </c>
-      <c r="B167">
+      <c r="B171">
         <v>2587.73</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A168" s="1">
+    <row r="172" spans="1:2">
+      <c r="A172" s="1">
         <v>44974</v>
       </c>
-      <c r="B168">
+      <c r="B172">
         <v>2571.5500000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A169" s="1">
+    <row r="173" spans="1:2">
+      <c r="A173" s="1">
         <v>44967</v>
       </c>
-      <c r="B169">
+      <c r="B173">
         <v>2432</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A170" s="1">
+    <row r="174" spans="1:2">
+      <c r="A174" s="1">
         <v>44960</v>
       </c>
-      <c r="B170">
+      <c r="B174">
         <v>2362.5700000000002</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A171" s="1">
+    <row r="175" spans="1:2">
+      <c r="A175" s="1">
         <v>44953</v>
       </c>
-      <c r="B171">
+      <c r="B175">
         <v>2239.69</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A172" s="1">
+    <row r="176" spans="1:2">
+      <c r="A176" s="1">
         <v>44946</v>
       </c>
-      <c r="B172">
+      <c r="B176">
         <v>2232.6</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A173" s="1">
+    <row r="177" spans="1:2">
+      <c r="A177" s="1">
         <v>44939</v>
       </c>
-      <c r="B173">
+      <c r="B177">
         <v>2231.16</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A174" s="1">
+    <row r="178" spans="1:2">
+      <c r="A178" s="1">
         <v>44932</v>
       </c>
-      <c r="B174">
+      <c r="B178">
         <v>2226.2600000000002</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A175" s="1">
+    <row r="179" spans="1:2">
+      <c r="A179" s="1">
         <v>44925</v>
       </c>
-      <c r="B175">
+      <c r="B179">
         <v>2196.61</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A176" s="1">
+    <row r="180" spans="1:2">
+      <c r="A180" s="1">
         <v>44918</v>
       </c>
-      <c r="B176">
+      <c r="B180">
         <v>2180.16</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A177" s="1">
+    <row r="181" spans="1:2">
+      <c r="A181" s="1">
         <v>44911</v>
       </c>
-      <c r="B177">
+      <c r="B181">
         <v>2192.5500000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A178" s="1">
+    <row r="182" spans="1:2">
+      <c r="A182" s="1">
         <v>44904</v>
       </c>
-      <c r="B178">
+      <c r="B182">
         <v>2193.12</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A179" s="1">
+    <row r="183" spans="1:2">
+      <c r="A183" s="1">
         <v>44897</v>
       </c>
-      <c r="B179">
+      <c r="B183">
         <v>2127.7199999999998</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A180" s="1">
+    <row r="184" spans="1:2">
+      <c r="A184" s="1">
         <v>44890</v>
       </c>
-      <c r="B180">
+      <c r="B184">
         <v>2073.58</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A181" s="1">
+    <row r="185" spans="1:2">
+      <c r="A185" s="1">
         <v>44883</v>
       </c>
-      <c r="B181">
+      <c r="B185">
         <v>2091.35</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A182" s="1">
+    <row r="186" spans="1:2">
+      <c r="A186" s="1">
         <v>44876</v>
       </c>
-      <c r="B182">
+      <c r="B186">
         <v>2029.94</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A183" s="1">
+    <row r="187" spans="1:2">
+      <c r="A187" s="1">
         <v>44869</v>
       </c>
-      <c r="B183">
+      <c r="B187">
         <v>2025.29</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A184" s="1">
+    <row r="188" spans="1:2">
+      <c r="A188" s="1">
         <v>44862</v>
       </c>
-      <c r="B184">
+      <c r="B188">
         <v>2046.68</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A185" s="1">
+    <row r="189" spans="1:2">
+      <c r="A189" s="1">
         <v>44855</v>
       </c>
-      <c r="B185">
+      <c r="B189">
         <v>2106.63</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A186" s="1">
+    <row r="190" spans="1:2">
+      <c r="A190" s="1">
         <v>44848</v>
       </c>
-      <c r="B186">
+      <c r="B190">
         <v>2168.94</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A187" s="1">
+    <row r="191" spans="1:2">
+      <c r="A191" s="1">
         <v>44841</v>
       </c>
-      <c r="B187">
+      <c r="B191">
         <v>2182.59</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A188" s="1">
+    <row r="192" spans="1:2">
+      <c r="A192" s="1">
         <v>44834</v>
       </c>
-      <c r="B188">
+      <c r="B192">
         <v>2261.71</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A189" s="1">
+    <row r="193" spans="1:2">
+      <c r="A193" s="1">
         <v>44827</v>
       </c>
-      <c r="B189">
+      <c r="B193">
         <v>2247.12</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A190" s="1">
+    <row r="194" spans="1:2">
+      <c r="A194" s="1">
         <v>44820</v>
       </c>
-      <c r="B190">
+      <c r="B194">
         <v>2233.71</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A191" s="1">
+    <row r="195" spans="1:2">
+      <c r="A195" s="1">
         <v>44813</v>
       </c>
-      <c r="B191">
+      <c r="B195">
         <v>2153.1799999999998</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A192" s="1">
+    <row r="196" spans="1:2">
+      <c r="A196" s="1">
         <v>44806</v>
       </c>
-      <c r="B192">
+      <c r="B196">
         <v>2131.16</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A193" s="1">
+    <row r="197" spans="1:2">
+      <c r="A197" s="1">
         <v>44799</v>
       </c>
-      <c r="B193">
+      <c r="B197">
         <v>2058.9699999999998</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A194" s="1">
+    <row r="198" spans="1:2">
+      <c r="A198" s="1">
         <v>44792</v>
       </c>
-      <c r="B194">
+      <c r="B198">
         <v>2024.96</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A195" s="1">
+    <row r="199" spans="1:2">
+      <c r="A199" s="1">
         <v>44785</v>
       </c>
-      <c r="B195">
+      <c r="B199">
         <v>1950.22</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A196" s="1">
+    <row r="200" spans="1:2">
+      <c r="A200" s="1">
         <v>44778</v>
       </c>
-      <c r="B196">
+      <c r="B200">
         <v>1928.69</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A197" s="1">
+    <row r="201" spans="1:2">
+      <c r="A201" s="1">
         <v>44771</v>
       </c>
-      <c r="B197">
+      <c r="B201">
         <v>1897.99</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A198" s="1">
+    <row r="202" spans="1:2">
+      <c r="A202" s="1">
         <v>44764</v>
       </c>
-      <c r="B198">
+      <c r="B202">
         <v>1954.38</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A199" s="1">
+    <row r="203" spans="1:2">
+      <c r="A203" s="1">
         <v>44757</v>
       </c>
-      <c r="B199">
+      <c r="B203">
         <v>1977.04</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A200" s="1">
+    <row r="204" spans="1:2">
+      <c r="A204" s="1">
         <v>44750</v>
       </c>
-      <c r="B200">
+      <c r="B204">
         <v>1990.82</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A201" s="1">
+    <row r="205" spans="1:2">
+      <c r="A205" s="1">
         <v>44743</v>
       </c>
-      <c r="B201">
+      <c r="B205">
         <v>2001.4</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A202" s="1">
+    <row r="206" spans="1:2">
+      <c r="A206" s="1">
         <v>44736</v>
       </c>
-      <c r="B202">
+      <c r="B206">
         <v>1988.44</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A203" s="1">
+    <row r="207" spans="1:2">
+      <c r="A207" s="1">
         <v>44729</v>
       </c>
-      <c r="B203">
+      <c r="B207">
         <v>1971.01</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A204" s="1">
+    <row r="208" spans="1:2">
+      <c r="A208" s="1">
         <v>44722</v>
       </c>
-      <c r="B204">
+      <c r="B208">
         <v>1916.24</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A205" s="1">
+    <row r="209" spans="1:2">
+      <c r="A209" s="1">
         <v>44715</v>
       </c>
-      <c r="B205">
+      <c r="B209">
         <v>1900.34</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A206" s="1">
+    <row r="210" spans="1:2">
+      <c r="A210" s="1">
         <v>44708</v>
       </c>
-      <c r="B206">
+      <c r="B210">
         <v>1911.04</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A207" s="1">
+    <row r="211" spans="1:2">
+      <c r="A211" s="1">
         <v>44701</v>
       </c>
-      <c r="B207">
+      <c r="B211">
         <v>1936.83</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A208" s="1">
+    <row r="212" spans="1:2">
+      <c r="A212" s="1">
         <v>44694</v>
       </c>
-      <c r="B208">
+      <c r="B212">
         <v>1919.93</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A209" s="1">
+    <row r="213" spans="1:2">
+      <c r="A213" s="1">
         <v>44687</v>
       </c>
-      <c r="B209">
+      <c r="B213">
         <v>1935.12</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A210" s="1">
+    <row r="214" spans="1:2">
+      <c r="A214" s="1">
         <v>44680</v>
       </c>
-      <c r="B210">
+      <c r="B214">
         <v>2000.04</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A211" s="1">
+    <row r="215" spans="1:2">
+      <c r="A215" s="1">
         <v>44673</v>
       </c>
-      <c r="B211">
+      <c r="B215">
         <v>1959.42</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A212" s="1">
+    <row r="216" spans="1:2">
+      <c r="A216" s="1">
         <v>44666</v>
       </c>
-      <c r="B212">
+      <c r="B216">
         <v>1931.16</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A213" s="1">
+    <row r="217" spans="1:2">
+      <c r="A217" s="1">
         <v>44659</v>
       </c>
-      <c r="B213">
+      <c r="B217">
         <v>1920.91</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A214" s="1">
+    <row r="218" spans="1:2">
+      <c r="A218" s="1">
         <v>44652</v>
       </c>
-      <c r="B214">
+      <c r="B218">
         <v>1947.63</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A215" s="1">
+    <row r="219" spans="1:2">
+      <c r="A219" s="1">
         <v>44645</v>
       </c>
-      <c r="B215">
+      <c r="B219">
         <v>1868.31</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A216" s="1">
+    <row r="220" spans="1:2">
+      <c r="A220" s="1">
         <v>44638</v>
       </c>
-      <c r="B216">
+      <c r="B220">
         <v>1825</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A217" s="1">
+    <row r="221" spans="1:2">
+      <c r="A221" s="1">
         <v>44631</v>
       </c>
-      <c r="B217">
+      <c r="B221">
         <v>1709.27</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A218" s="1">
+    <row r="222" spans="1:2">
+      <c r="A222" s="1">
         <v>44624</v>
       </c>
-      <c r="B218">
+      <c r="B222">
         <v>1473.44</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A219" s="1">
+    <row r="223" spans="1:2">
+      <c r="A223" s="1">
         <v>44617</v>
       </c>
-      <c r="B219">
+      <c r="B223">
         <v>1362.98</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A220" s="1">
+    <row r="224" spans="1:2">
+      <c r="A224" s="1">
         <v>44610</v>
       </c>
-      <c r="B220">
+      <c r="B224">
         <v>1337.31</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A221" s="1">
+    <row r="225" spans="1:2">
+      <c r="A225" s="1">
         <v>44603</v>
       </c>
-      <c r="B221">
+      <c r="B225">
         <v>1283.06</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A222" s="1">
+    <row r="226" spans="1:2">
+      <c r="A226" s="1">
         <v>44596</v>
       </c>
-      <c r="B222">
+      <c r="B226">
         <v>1289.22</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A223" s="1">
+    <row r="227" spans="1:2">
+      <c r="A227" s="1">
         <v>44589</v>
       </c>
-      <c r="B223">
+      <c r="B227">
         <v>1287.8399999999999</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A224" s="1">
+    <row r="228" spans="1:2">
+      <c r="A228" s="1">
         <v>44582</v>
       </c>
-      <c r="B224">
+      <c r="B228">
         <v>1301.78</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A225" s="1">
+    <row r="229" spans="1:2">
+      <c r="A229" s="1">
         <v>44575</v>
       </c>
-      <c r="B225">
+      <c r="B229">
         <v>1302.52</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A226" s="1">
+    <row r="230" spans="1:2">
+      <c r="A230" s="1">
         <v>44568</v>
       </c>
-      <c r="B226">
+      <c r="B230">
         <v>1313.3</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A227" s="1">
+    <row r="231" spans="1:2">
+      <c r="A231" s="1">
         <v>44561</v>
       </c>
-      <c r="B227">
+      <c r="B231">
         <v>1309.25</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A228" s="1">
+    <row r="232" spans="1:2">
+      <c r="A232" s="1">
         <v>44554</v>
       </c>
-      <c r="B228">
+      <c r="B232">
         <v>1308.1600000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A229" s="1">
+    <row r="233" spans="1:2">
+      <c r="A233" s="1">
         <v>44547</v>
       </c>
-      <c r="B229">
+      <c r="B233">
         <v>1322.88</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A230" s="1">
+    <row r="234" spans="1:2">
+      <c r="A234" s="1">
         <v>44540</v>
       </c>
-      <c r="B230">
+      <c r="B234">
         <v>1309.21</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A231" s="1">
+    <row r="235" spans="1:2">
+      <c r="A235" s="1">
         <v>44533</v>
       </c>
-      <c r="B231">
+      <c r="B235">
         <v>1314.94</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A232" s="1">
+    <row r="236" spans="1:2">
+      <c r="A236" s="1">
         <v>44526</v>
       </c>
-      <c r="B232">
+      <c r="B236">
         <v>1306.75</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A233" s="1">
+    <row r="237" spans="1:2">
+      <c r="A237" s="1">
         <v>44519</v>
       </c>
-      <c r="B233">
+      <c r="B237">
         <v>1281.03</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A234" s="1">
+    <row r="238" spans="1:2">
+      <c r="A238" s="1">
         <v>44512</v>
       </c>
-      <c r="B234">
+      <c r="B238">
         <v>1269.2</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A235" s="1">
+    <row r="239" spans="1:2">
+      <c r="A239" s="1">
         <v>44505</v>
       </c>
-      <c r="B235">
+      <c r="B239">
         <v>1259.8399999999999</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A236" s="1">
+    <row r="240" spans="1:2">
+      <c r="A240" s="1">
         <v>44498</v>
       </c>
-      <c r="B236">
+      <c r="B240">
         <v>1245.18</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A237" s="1">
+    <row r="241" spans="1:2">
+      <c r="A241" s="1">
         <v>44491</v>
       </c>
-      <c r="B237">
+      <c r="B241">
         <v>1243.06</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A238" s="1">
+    <row r="242" spans="1:2">
+      <c r="A242" s="1">
         <v>44484</v>
       </c>
-      <c r="B238">
+      <c r="B242">
         <v>1247.95</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A239" s="1">
+    <row r="243" spans="1:2">
+      <c r="A243" s="1">
         <v>44477</v>
       </c>
-      <c r="B239">
+      <c r="B243">
         <v>1274.79</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A240" s="1">
+    <row r="244" spans="1:2">
+      <c r="A244" s="1">
         <v>44470</v>
       </c>
-      <c r="B240">
+      <c r="B244">
         <v>1320.32</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A241" s="1">
+    <row r="245" spans="1:2">
+      <c r="A245" s="1">
         <v>44463</v>
       </c>
-      <c r="B241">
+      <c r="B245">
         <v>1335.83</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A242" s="1">
+    <row r="246" spans="1:2">
+      <c r="A246" s="1">
         <v>44456</v>
       </c>
-      <c r="B242">
+      <c r="B246">
         <v>1351.71</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A243" s="1">
+    <row r="247" spans="1:2">
+      <c r="A247" s="1">
         <v>44449</v>
       </c>
-      <c r="B243">
+      <c r="B247">
         <v>1354.98</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A244" s="1">
+    <row r="248" spans="1:2">
+      <c r="A248" s="1">
         <v>44442</v>
       </c>
-      <c r="B244">
+      <c r="B248">
         <v>1385.35</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A245" s="1">
+    <row r="249" spans="1:2">
+      <c r="A249" s="1">
         <v>44435</v>
       </c>
-      <c r="B245">
+      <c r="B249">
         <v>1411.31</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A246" s="1">
+    <row r="250" spans="1:2">
+      <c r="A250" s="1">
         <v>44428</v>
       </c>
-      <c r="B246">
+      <c r="B250">
         <v>1477.45</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A247" s="1">
+    <row r="251" spans="1:2">
+      <c r="A251" s="1">
         <v>44421</v>
       </c>
-      <c r="B247">
+      <c r="B251">
         <v>1496.25</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A248" s="1">
+    <row r="252" spans="1:2">
+      <c r="A252" s="1">
         <v>44414</v>
       </c>
-      <c r="B248">
+      <c r="B252">
         <v>1519.75</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A249" s="1">
+    <row r="253" spans="1:2">
+      <c r="A253" s="1">
         <v>44407</v>
       </c>
-      <c r="B249">
+      <c r="B253">
         <v>1555.15</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A250" s="1">
+    <row r="254" spans="1:2">
+      <c r="A254" s="1">
         <v>44400</v>
       </c>
-      <c r="B250">
+      <c r="B254">
         <v>1554.7</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A251" s="1">
+    <row r="255" spans="1:2">
+      <c r="A255" s="1">
         <v>44393</v>
       </c>
-      <c r="B251">
+      <c r="B255">
         <v>1579.18</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A252" s="1">
+    <row r="256" spans="1:2">
+      <c r="A256" s="1">
         <v>44386</v>
       </c>
-      <c r="B252">
+      <c r="B256">
         <v>1592.52</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A253" s="1">
+    <row r="257" spans="1:2">
+      <c r="A257" s="1">
         <v>44379</v>
       </c>
-      <c r="B253">
+      <c r="B257">
         <v>1568.18</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A254" s="1">
+    <row r="258" spans="1:2">
+      <c r="A258" s="1">
         <v>44372</v>
       </c>
-      <c r="B254">
+      <c r="B258">
         <v>1591.59</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A255" s="1">
+    <row r="259" spans="1:2">
+      <c r="A259" s="1">
         <v>44365</v>
       </c>
-      <c r="B255">
+      <c r="B259">
         <v>1618.25</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A256" s="1">
+    <row r="260" spans="1:2">
+      <c r="A260" s="1">
         <v>44358</v>
       </c>
-      <c r="B256">
+      <c r="B260">
         <v>1640.09</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A257" s="1">
+    <row r="261" spans="1:2">
+      <c r="A261" s="1">
         <v>44351</v>
       </c>
-      <c r="B257">
+      <c r="B261">
         <v>1629.39</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A258" s="1">
+    <row r="262" spans="1:2">
+      <c r="A262" s="1">
         <v>44344</v>
       </c>
-      <c r="B258">
+      <c r="B262">
         <v>1627.2</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A259" s="1">
+    <row r="263" spans="1:2">
+      <c r="A263" s="1">
         <v>44337</v>
       </c>
-      <c r="B259">
+      <c r="B263">
         <v>1604.37</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A260" s="1">
+    <row r="264" spans="1:2">
+      <c r="A264" s="1">
         <v>44330</v>
       </c>
-      <c r="B260">
+      <c r="B264">
         <v>1503.76</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A261" s="1">
+    <row r="265" spans="1:2">
+      <c r="A265" s="1">
         <v>44323</v>
       </c>
-      <c r="B261">
+      <c r="B265">
         <v>1477.37</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A262" s="1">
+    <row r="266" spans="1:2">
+      <c r="A266" s="1">
         <v>44316</v>
       </c>
-      <c r="B262">
+      <c r="B266">
         <v>1481.24</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A263" s="1">
+    <row r="267" spans="1:2">
+      <c r="A267" s="1">
         <v>44309</v>
       </c>
-      <c r="B263">
+      <c r="B267">
         <v>1520.35</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A264" s="1">
+    <row r="268" spans="1:2">
+      <c r="A268" s="1">
         <v>44302</v>
       </c>
-      <c r="B264">
+      <c r="B268">
         <v>1559.84</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A265" s="1">
+    <row r="269" spans="1:2">
+      <c r="A269" s="1">
         <v>44295</v>
       </c>
-      <c r="B265">
+      <c r="B269">
         <v>1577.04</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A266" s="1">
+    <row r="270" spans="1:2">
+      <c r="A270" s="1">
         <v>44288</v>
       </c>
-      <c r="B266">
+      <c r="B270">
         <v>1562.4</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A267" s="1">
+    <row r="271" spans="1:2">
+      <c r="A271" s="1">
         <v>44281</v>
       </c>
-      <c r="B267">
+      <c r="B271">
         <v>1577.66</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A268" s="1">
+    <row r="272" spans="1:2">
+      <c r="A272" s="1">
         <v>44274</v>
       </c>
-      <c r="B268">
+      <c r="B272">
         <v>1581.37</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A269" s="1">
+    <row r="273" spans="1:2">
+      <c r="A273" s="1">
         <v>44267</v>
       </c>
-      <c r="B269">
+      <c r="B273">
         <v>1520.37</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A270" s="1">
+    <row r="274" spans="1:2">
+      <c r="A274" s="1">
         <v>44260</v>
       </c>
-      <c r="B270">
+      <c r="B274">
         <v>1429.13</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A271" s="1">
+    <row r="275" spans="1:2">
+      <c r="A275" s="1">
         <v>44253</v>
       </c>
-      <c r="B271">
+      <c r="B275">
         <v>1374.16</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A272" s="1">
+    <row r="276" spans="1:2">
+      <c r="A276" s="1">
         <v>44246</v>
       </c>
-      <c r="B272">
+      <c r="B276">
         <v>1286.3699999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A273" s="1">
+    <row r="277" spans="1:2">
+      <c r="A277" s="1">
         <v>44239</v>
       </c>
-      <c r="B273">
+      <c r="B277">
         <v>1273.82</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A274" s="1">
+    <row r="278" spans="1:2">
+      <c r="A278" s="1">
         <v>44232</v>
       </c>
-      <c r="B274">
+      <c r="B278">
         <v>1272.82</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A275" s="1">
+    <row r="279" spans="1:2">
+      <c r="A279" s="1">
         <v>44225</v>
       </c>
-      <c r="B275">
+      <c r="B279">
         <v>1294.05</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A276" s="1">
+    <row r="280" spans="1:2">
+      <c r="A280" s="1">
         <v>44218</v>
       </c>
-      <c r="B276">
+      <c r="B280">
         <v>1288.1400000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A277" s="1">
+    <row r="281" spans="1:2">
+      <c r="A281" s="1">
         <v>44211</v>
       </c>
-      <c r="B277">
+      <c r="B281">
         <v>1283.98</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A278" s="1">
+    <row r="282" spans="1:2">
+      <c r="A282" s="1">
         <v>44204</v>
       </c>
-      <c r="B278">
+      <c r="B282">
         <v>1273.45</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A279" s="1">
+    <row r="283" spans="1:2">
+      <c r="A283" s="1">
         <v>44197</v>
       </c>
-      <c r="B279">
+      <c r="B283">
         <v>1298.8699999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A280" s="1">
+    <row r="284" spans="1:2">
+      <c r="A284" s="1">
         <v>44190</v>
       </c>
-      <c r="B280">
+      <c r="B284">
         <v>1301.8599999999999</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A281" s="1">
+    <row r="285" spans="1:2">
+      <c r="A285" s="1">
         <v>44183</v>
       </c>
-      <c r="B281">
+      <c r="B285">
         <v>1301.97</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A282" s="1">
+    <row r="286" spans="1:2">
+      <c r="A286" s="1">
         <v>44176</v>
       </c>
-      <c r="B282">
+      <c r="B286">
         <v>1317.71</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A283" s="1">
+    <row r="287" spans="1:2">
+      <c r="A287" s="1">
         <v>44169</v>
       </c>
-      <c r="B283">
+      <c r="B287">
         <v>1313.42</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A284" s="1">
+    <row r="288" spans="1:2">
+      <c r="A288" s="1">
         <v>44162</v>
       </c>
-      <c r="B284">
+      <c r="B288">
         <v>1304.8</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A285" s="1">
+    <row r="289" spans="1:2">
+      <c r="A289" s="1">
         <v>44155</v>
       </c>
-      <c r="B285">
+      <c r="B289">
         <v>1356.82</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A286" s="1">
+    <row r="290" spans="1:2">
+      <c r="A290" s="1">
         <v>44148</v>
       </c>
-      <c r="B286">
+      <c r="B290">
         <v>1422.51</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A287" s="1">
+    <row r="291" spans="1:2">
+      <c r="A291" s="1">
         <v>44141</v>
       </c>
-      <c r="B287">
+      <c r="B291">
         <v>1428</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A288" s="1">
+    <row r="292" spans="1:2">
+      <c r="A292" s="1">
         <v>44134</v>
       </c>
-      <c r="B288">
+      <c r="B292">
         <v>1463.97</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A289" s="1">
+    <row r="293" spans="1:2">
+      <c r="A293" s="1">
         <v>44127</v>
       </c>
-      <c r="B289">
+      <c r="B293">
         <v>1441.41</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A290" s="1">
+    <row r="294" spans="1:2">
+      <c r="A294" s="1">
         <v>44120</v>
       </c>
-      <c r="B290">
+      <c r="B294">
         <v>1445.44</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A291" s="1">
+    <row r="295" spans="1:2">
+      <c r="A295" s="1">
         <v>44113</v>
       </c>
-      <c r="B291">
+      <c r="B295">
         <v>1425.08</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A292" s="1">
+    <row r="296" spans="1:2">
+      <c r="A296" s="1">
         <v>44106</v>
       </c>
-      <c r="B292">
+      <c r="B296">
         <v>1442.94</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A293" s="1">
+    <row r="297" spans="1:2">
+      <c r="A297" s="1">
         <v>44099</v>
       </c>
-      <c r="B293">
+      <c r="B297">
         <v>1478.61</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A294" s="1">
+    <row r="298" spans="1:2">
+      <c r="A298" s="1">
         <v>44092</v>
       </c>
-      <c r="B294">
+      <c r="B298">
         <v>1429.57</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A295" s="1">
+    <row r="299" spans="1:2">
+      <c r="A299" s="1">
         <v>44085</v>
       </c>
-      <c r="B295">
+      <c r="B299">
         <v>1585.9</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A296" s="1">
+    <row r="300" spans="1:2">
+      <c r="A300" s="1">
         <v>44078</v>
       </c>
-      <c r="B296">
+      <c r="B300">
         <v>1611.07</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A297" s="1">
+    <row r="301" spans="1:2">
+      <c r="A301" s="1">
         <v>44071</v>
       </c>
-      <c r="B297">
+      <c r="B301">
         <v>1594.97</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A298" s="1">
+    <row r="302" spans="1:2">
+      <c r="A302" s="1">
         <v>44064</v>
       </c>
-      <c r="B298">
+      <c r="B302">
         <v>1622.78</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A299" s="1">
+    <row r="303" spans="1:2">
+      <c r="A303" s="1">
         <v>44057</v>
       </c>
-      <c r="B299">
+      <c r="B303">
         <v>1603.81</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A300" s="1">
+    <row r="304" spans="1:2">
+      <c r="A304" s="1">
         <v>44050</v>
       </c>
-      <c r="B300">
+      <c r="B304">
         <v>1622.32</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A301" s="1">
+    <row r="305" spans="1:2">
+      <c r="A305" s="1">
         <v>44043</v>
       </c>
-      <c r="B301">
+      <c r="B305">
         <v>1632.33</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A302" s="1">
+    <row r="306" spans="1:2">
+      <c r="A306" s="1">
         <v>44036</v>
       </c>
-      <c r="B302">
+      <c r="B306">
         <v>1623.55</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A303" s="1">
+    <row r="307" spans="1:2">
+      <c r="A307" s="1">
         <v>44029</v>
       </c>
-      <c r="B303">
+      <c r="B307">
         <v>1612.18</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A304" s="1">
+    <row r="308" spans="1:2">
+      <c r="A308" s="1">
         <v>44022</v>
       </c>
-      <c r="B304">
+      <c r="B308">
         <v>1701.45</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A305" s="1">
+    <row r="309" spans="1:2">
+      <c r="A309" s="1">
         <v>44015</v>
       </c>
-      <c r="B305">
+      <c r="B309">
         <v>1792.91</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A306" s="1">
+    <row r="310" spans="1:2">
+      <c r="A310" s="1">
         <v>44008</v>
       </c>
-      <c r="B306">
+      <c r="B310">
         <v>1872.65</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A307" s="1">
+    <row r="311" spans="1:2">
+      <c r="A311" s="1">
         <v>44001</v>
       </c>
-      <c r="B307">
+      <c r="B311">
         <v>1848.67</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A308" s="1">
+    <row r="312" spans="1:2">
+      <c r="A312" s="1">
         <v>43994</v>
       </c>
-      <c r="B308">
+      <c r="B312">
         <v>1871.44</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A309" s="1">
+    <row r="313" spans="1:2">
+      <c r="A313" s="1">
         <v>43987</v>
       </c>
-      <c r="B309">
+      <c r="B313">
         <v>1805.93</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A310" s="1">
+    <row r="314" spans="1:2">
+      <c r="A314" s="1">
         <v>43980</v>
       </c>
-      <c r="B310">
+      <c r="B314">
         <v>1849.51</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A311" s="1">
+    <row r="315" spans="1:2">
+      <c r="A315" s="1">
         <v>43973</v>
       </c>
-      <c r="B311">
+      <c r="B315">
         <v>1843.17</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A312" s="1">
+    <row r="316" spans="1:2">
+      <c r="A316" s="1">
         <v>43966</v>
       </c>
-      <c r="B312">
+      <c r="B316">
         <v>1839.52</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A313" s="1">
+    <row r="317" spans="1:2">
+      <c r="A317" s="1">
         <v>43959</v>
       </c>
-      <c r="B313">
+      <c r="B317">
         <v>1887.61</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A314" s="1">
+    <row r="318" spans="1:2">
+      <c r="A318" s="1">
         <v>43952</v>
       </c>
-      <c r="B314">
+      <c r="B318">
         <v>2033.1</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A315" s="1">
+    <row r="319" spans="1:2">
+      <c r="A319" s="1">
         <v>43945</v>
       </c>
-      <c r="B315">
+      <c r="B319">
         <v>2127.9</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A316" s="1">
+    <row r="320" spans="1:2">
+      <c r="A320" s="1">
         <v>43938</v>
       </c>
-      <c r="B316">
+      <c r="B320">
         <v>2130.98</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A317" s="1">
+    <row r="321" spans="1:2">
+      <c r="A321" s="1">
         <v>43931</v>
       </c>
-      <c r="B317">
+      <c r="B321">
         <v>2151.8200000000002</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A318" s="1">
+    <row r="322" spans="1:2">
+      <c r="A322" s="1">
         <v>43924</v>
       </c>
-      <c r="B318">
+      <c r="B322">
         <v>2231.61</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A319" s="1">
+    <row r="323" spans="1:2">
+      <c r="A323" s="1">
         <v>43917</v>
       </c>
-      <c r="B319">
+      <c r="B323">
         <v>2257.73</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A320" s="1">
+    <row r="324" spans="1:2">
+      <c r="A324" s="1">
         <v>43910</v>
       </c>
-      <c r="B320">
+      <c r="B324">
         <v>2481.52</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A321" s="1">
+    <row r="325" spans="1:2">
+      <c r="A325" s="1">
         <v>43903</v>
       </c>
-      <c r="B321">
+      <c r="B325">
         <v>2284.9299999999998</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A322" s="1">
+    <row r="326" spans="1:2">
+      <c r="A326" s="1">
         <v>43896</v>
       </c>
-      <c r="B322">
+      <c r="B326">
         <v>2173.83</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A323" s="1">
+    <row r="327" spans="1:2">
+      <c r="A327" s="1">
         <v>43889</v>
       </c>
-      <c r="B323">
+      <c r="B327">
         <v>2135.73</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A324" s="1">
+    <row r="328" spans="1:2">
+      <c r="A328" s="1">
         <v>43882</v>
       </c>
-      <c r="B324">
+      <c r="B328">
         <v>2010.76</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A325" s="1">
+    <row r="329" spans="1:2">
+      <c r="A329" s="1">
         <v>43875</v>
       </c>
-      <c r="B325">
+      <c r="B329">
         <v>1946.28</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A326" s="1">
+    <row r="330" spans="1:2">
+      <c r="A330" s="1">
         <v>43868</v>
       </c>
-      <c r="B326">
+      <c r="B330">
         <v>1935.94</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A327" s="1">
+    <row r="331" spans="1:2">
+      <c r="A331" s="1">
         <v>43861</v>
       </c>
-      <c r="B327">
+      <c r="B331">
         <v>1926.68</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A328" s="1">
+    <row r="332" spans="1:2">
+      <c r="A332" s="1">
         <v>43854</v>
       </c>
-      <c r="B328">
+      <c r="B332">
         <v>1871.27</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A329" s="1">
+    <row r="333" spans="1:2">
+      <c r="A333" s="1">
         <v>43847</v>
       </c>
-      <c r="B329">
+      <c r="B333">
         <v>1872.57</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A330" s="1">
+    <row r="334" spans="1:2">
+      <c r="A334" s="1">
         <v>43840</v>
       </c>
-      <c r="B330">
+      <c r="B334">
         <v>1933.16</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A331" s="1">
+    <row r="335" spans="1:2">
+      <c r="A335" s="1">
         <v>43833</v>
       </c>
-      <c r="B331">
+      <c r="B335">
         <v>1975.22</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A332" s="1">
+    <row r="336" spans="1:2">
+      <c r="A336" s="1">
         <v>43826</v>
       </c>
-      <c r="B332">
+      <c r="B336">
         <v>1981.54</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A333" s="1">
+    <row r="337" spans="1:2">
+      <c r="A337" s="1">
         <v>43819</v>
       </c>
-      <c r="B333">
+      <c r="B337">
         <v>2030.89</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A334" s="1">
+    <row r="338" spans="1:2">
+      <c r="A338" s="1">
         <v>43812</v>
       </c>
-      <c r="B334">
+      <c r="B338">
         <v>2094.6799999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A335" s="1">
+    <row r="339" spans="1:2">
+      <c r="A339" s="1">
         <v>43805</v>
       </c>
-      <c r="B335">
+      <c r="B339">
         <v>2086.14</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A336" s="1">
+    <row r="340" spans="1:2">
+      <c r="A340" s="1">
         <v>43798</v>
       </c>
-      <c r="B336">
+      <c r="B340">
         <v>2059.2600000000002</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A337" s="1">
+    <row r="341" spans="1:2">
+      <c r="A341" s="1">
         <v>43791</v>
       </c>
-      <c r="B337">
+      <c r="B341">
         <v>1992.29</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A338" s="1">
+    <row r="342" spans="1:2">
+      <c r="A342" s="1">
         <v>43784</v>
       </c>
-      <c r="B338">
+      <c r="B342">
         <v>1926.99</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A339" s="1">
+    <row r="343" spans="1:2">
+      <c r="A343" s="1">
         <v>43777</v>
       </c>
-      <c r="B339">
+      <c r="B343">
         <v>1916.98</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A340" s="1">
+    <row r="344" spans="1:2">
+      <c r="A344" s="1">
         <v>43770</v>
       </c>
-      <c r="B340">
+      <c r="B344">
         <v>1932.05</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A341" s="1">
+    <row r="345" spans="1:2">
+      <c r="A345" s="1">
         <v>43763</v>
       </c>
-      <c r="B341">
+      <c r="B345">
         <v>1938.9</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A342" s="1">
+    <row r="346" spans="1:2">
+      <c r="A346" s="1">
         <v>43756</v>
       </c>
-      <c r="B342">
+      <c r="B346">
         <v>1947.83</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A343" s="1">
+    <row r="347" spans="1:2">
+      <c r="A347" s="1">
         <v>43749</v>
       </c>
-      <c r="B343">
+      <c r="B347">
         <v>1905.78</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A344" s="1">
+    <row r="348" spans="1:2">
+      <c r="A348" s="1">
         <v>43742</v>
       </c>
-      <c r="B344">
+      <c r="B348">
         <v>1901.43</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A345" s="1">
+    <row r="349" spans="1:2">
+      <c r="A349" s="1">
         <v>43735</v>
       </c>
-      <c r="B345">
+      <c r="B349">
         <v>1892.53</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A346" s="1">
+    <row r="350" spans="1:2">
+      <c r="A350" s="1">
         <v>43728</v>
       </c>
-      <c r="B346">
+      <c r="B350">
         <v>1896.04</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A347" s="1">
+    <row r="351" spans="1:2">
+      <c r="A351" s="1">
         <v>43721</v>
       </c>
-      <c r="B347">
+      <c r="B351">
         <v>1891.07</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A348" s="1">
+    <row r="352" spans="1:2">
+      <c r="A352" s="1">
         <v>43714</v>
       </c>
-      <c r="B348">
+      <c r="B352">
         <v>1885.63</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A349" s="1">
+    <row r="353" spans="1:2">
+      <c r="A353" s="1">
         <v>43707</v>
       </c>
-      <c r="B349">
+      <c r="B353">
         <v>1905.11</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A350" s="1">
+    <row r="354" spans="1:2">
+      <c r="A354" s="1">
         <v>43700</v>
       </c>
-      <c r="B350">
+      <c r="B354">
         <v>1909.29</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A351" s="1">
+    <row r="355" spans="1:2">
+      <c r="A355" s="1">
         <v>43693</v>
       </c>
-      <c r="B351">
+      <c r="B355">
         <v>1910.12</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A352" s="1">
+    <row r="356" spans="1:2">
+      <c r="A356" s="1">
         <v>43686</v>
       </c>
-      <c r="B352">
+      <c r="B356">
         <v>1861.33</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A353" s="1">
+    <row r="357" spans="1:2">
+      <c r="A357" s="1">
         <v>43679</v>
       </c>
-      <c r="B353">
+      <c r="B357">
         <v>1796.06</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A354" s="1">
+    <row r="358" spans="1:2">
+      <c r="A358" s="1">
         <v>43672</v>
       </c>
-      <c r="B354">
+      <c r="B358">
         <v>1738.54</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A355" s="1">
+    <row r="359" spans="1:2">
+      <c r="A359" s="1">
         <v>43665</v>
       </c>
-      <c r="B355">
+      <c r="B359">
         <v>1737.49</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A356" s="1">
+    <row r="360" spans="1:2">
+      <c r="A360" s="1">
         <v>43658</v>
       </c>
-      <c r="B356">
+      <c r="B360">
         <v>1777.87</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A357" s="1">
+    <row r="361" spans="1:2">
+      <c r="A361" s="1">
         <v>43651</v>
       </c>
-      <c r="B357">
+      <c r="B361">
         <v>1815.34</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A358" s="1">
+    <row r="362" spans="1:2">
+      <c r="A362" s="1">
         <v>43644</v>
       </c>
-      <c r="B358">
+      <c r="B362">
         <v>1822.16</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A359" s="1">
+    <row r="363" spans="1:2">
+      <c r="A363" s="1">
         <v>43637</v>
       </c>
-      <c r="B359">
+      <c r="B363">
         <v>1818.95</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A360" s="1">
+    <row r="364" spans="1:2">
+      <c r="A364" s="1">
         <v>43630</v>
       </c>
-      <c r="B360">
+      <c r="B364">
         <v>1835.57</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A361" s="1">
+    <row r="365" spans="1:2">
+      <c r="A365" s="1">
         <v>43623</v>
       </c>
-      <c r="B361">
+      <c r="B365">
         <v>1822.65</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A362" s="1">
+    <row r="366" spans="1:2">
+      <c r="A366" s="1">
         <v>43616</v>
       </c>
-      <c r="B362">
+      <c r="B366">
         <v>1807.31</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A363" s="1">
+    <row r="367" spans="1:2">
+      <c r="A367" s="1">
         <v>43609</v>
       </c>
-      <c r="B363">
+      <c r="B367">
         <v>1802.01</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A364" s="1">
+    <row r="368" spans="1:2">
+      <c r="A368" s="1">
         <v>43602</v>
       </c>
-      <c r="B364">
+      <c r="B368">
         <v>1793.25</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A365" s="1">
+    <row r="369" spans="1:2">
+      <c r="A369" s="1">
         <v>43595</v>
       </c>
-      <c r="B365">
+      <c r="B369">
         <v>1757.51</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A366" s="1">
+    <row r="370" spans="1:2">
+      <c r="A370" s="1">
         <v>43588</v>
       </c>
-      <c r="B366">
+      <c r="B370">
         <v>1737.27</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A367" s="1">
+    <row r="371" spans="1:2">
+      <c r="A371" s="1">
         <v>43581</v>
       </c>
-      <c r="B367">
+      <c r="B371">
         <v>1724.37</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A368" s="1">
+    <row r="372" spans="1:2">
+      <c r="A372" s="1">
         <v>43574</v>
       </c>
-      <c r="B368">
+      <c r="B372">
         <v>1700.75</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A369" s="1">
+    <row r="373" spans="1:2">
+      <c r="A373" s="1">
         <v>43567</v>
       </c>
-      <c r="B369">
+      <c r="B373">
         <v>1693.16</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A370" s="1">
+    <row r="374" spans="1:2">
+      <c r="A374" s="1">
         <v>43560</v>
       </c>
-      <c r="B370">
+      <c r="B374">
         <v>1645.82</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A371" s="1">
+    <row r="375" spans="1:2">
+      <c r="A375" s="1">
         <v>43553</v>
       </c>
-      <c r="B371">
+      <c r="B375">
         <v>1547.58</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A372" s="1">
+    <row r="376" spans="1:2">
+      <c r="A376" s="1">
         <v>43546</v>
       </c>
-      <c r="B372">
+      <c r="B376">
         <v>1463.33</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A373" s="1">
+    <row r="377" spans="1:2">
+      <c r="A377" s="1">
         <v>43539</v>
       </c>
-      <c r="B373">
+      <c r="B377">
         <v>1414.44</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A374" s="1">
+    <row r="378" spans="1:2">
+      <c r="A378" s="1">
         <v>43532</v>
       </c>
-      <c r="B374">
+      <c r="B378">
         <v>1424.34</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A375" s="1">
+    <row r="379" spans="1:2">
+      <c r="A379" s="1">
         <v>43525</v>
       </c>
-      <c r="B375">
+      <c r="B379">
         <v>1410.95</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A376" s="1">
+    <row r="380" spans="1:2">
+      <c r="A380" s="1">
         <v>43518</v>
       </c>
-      <c r="B376">
+      <c r="B380">
         <v>1406.23</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A377" s="1">
+    <row r="381" spans="1:2">
+      <c r="A381" s="1">
         <v>43511</v>
       </c>
-      <c r="B377">
+      <c r="B381">
         <v>1400.46</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A378" s="1">
+    <row r="382" spans="1:2">
+      <c r="A382" s="1">
         <v>43504</v>
       </c>
-      <c r="B378">
+      <c r="B382">
         <v>1387.41</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A379" s="1">
+    <row r="383" spans="1:2">
+      <c r="A383" s="1">
         <v>43497</v>
       </c>
-      <c r="B379">
+      <c r="B383">
         <v>1357.73</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A380" s="1">
+    <row r="384" spans="1:2">
+      <c r="A384" s="1">
         <v>43490</v>
       </c>
-      <c r="B380">
+      <c r="B384">
         <v>1363.46</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A381" s="1">
+    <row r="385" spans="1:2">
+      <c r="A385" s="1">
         <v>43483</v>
       </c>
-      <c r="B381">
+      <c r="B385">
         <v>1361.38</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A382" s="1">
+    <row r="386" spans="1:2">
+      <c r="A386" s="1">
         <v>43476</v>
       </c>
-      <c r="B382">
+      <c r="B386">
         <v>1369.73</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A383" s="1">
+    <row r="387" spans="1:2">
+      <c r="A387" s="1">
         <v>43469</v>
       </c>
-      <c r="B383">
+      <c r="B387">
         <v>1374.05</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A384" s="1">
+    <row r="388" spans="1:2">
+      <c r="A388" s="1">
         <v>43462</v>
       </c>
-      <c r="B384">
+      <c r="B388">
         <v>1402.49</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A385" s="1">
+    <row r="389" spans="1:2">
+      <c r="A389" s="1">
         <v>43455</v>
       </c>
-      <c r="B385">
+      <c r="B389">
         <v>1396.95</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A386" s="1">
+    <row r="390" spans="1:2">
+      <c r="A390" s="1">
         <v>43448</v>
       </c>
-      <c r="B386">
+      <c r="B390">
         <v>1368.73</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A387" s="1">
+    <row r="391" spans="1:2">
+      <c r="A391" s="1">
         <v>43441</v>
       </c>
-      <c r="B387">
+      <c r="B391">
         <v>1354.61</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A388" s="1">
+    <row r="392" spans="1:2">
+      <c r="A392" s="1">
         <v>43434</v>
       </c>
-      <c r="B388">
+      <c r="B392">
         <v>1364.06</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A389" s="1">
+    <row r="393" spans="1:2">
+      <c r="A393" s="1">
         <v>43427</v>
       </c>
-      <c r="B389">
+      <c r="B393">
         <v>1368.69</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A390" s="1">
+    <row r="394" spans="1:2">
+      <c r="A394" s="1">
         <v>43420</v>
       </c>
-      <c r="B390">
+      <c r="B394">
         <v>1350.56</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A391" s="1">
+    <row r="395" spans="1:2">
+      <c r="A395" s="1">
         <v>43413</v>
       </c>
-      <c r="B391">
+      <c r="B395">
         <v>1342.32</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A392" s="1">
+    <row r="396" spans="1:2">
+      <c r="A396" s="1">
         <v>43406</v>
       </c>
-      <c r="B392">
+      <c r="B396">
         <v>1338.71</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A393" s="1">
+    <row r="397" spans="1:2">
+      <c r="A397" s="1">
         <v>43399</v>
       </c>
-      <c r="B393">
+      <c r="B397">
         <v>1333.57</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A394" s="1">
+    <row r="398" spans="1:2">
+      <c r="A398" s="1">
         <v>43392</v>
       </c>
-      <c r="B394">
+      <c r="B398">
         <v>1330.92</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A395" s="1">
+    <row r="399" spans="1:2">
+      <c r="A399" s="1">
         <v>43385</v>
       </c>
-      <c r="B395">
+      <c r="B399">
         <v>1338.28</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A396" s="1">
+    <row r="400" spans="1:2">
+      <c r="A400" s="1">
         <v>43378</v>
       </c>
-      <c r="B396">
+      <c r="B400">
         <v>1369.18</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A397" s="1">
+    <row r="401" spans="1:2">
+      <c r="A401" s="1">
         <v>43371</v>
       </c>
-      <c r="B397">
+      <c r="B401">
         <v>1367.75</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A398" s="1">
+    <row r="402" spans="1:2">
+      <c r="A402" s="1">
         <v>43364</v>
       </c>
-      <c r="B398">
+      <c r="B402">
         <v>1404.93</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A399" s="1">
+    <row r="403" spans="1:2">
+      <c r="A403" s="1">
         <v>43357</v>
       </c>
-      <c r="B399">
+      <c r="B403">
         <v>1447.35</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A400" s="1">
+    <row r="404" spans="1:2">
+      <c r="A404" s="1">
         <v>43350</v>
       </c>
-      <c r="B400">
+      <c r="B404">
         <v>1526.72</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A401" s="1">
+    <row r="405" spans="1:2">
+      <c r="A405" s="1">
         <v>43343</v>
       </c>
-      <c r="B401">
+      <c r="B405">
         <v>1553.14</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A402" s="1">
+    <row r="406" spans="1:2">
+      <c r="A406" s="1">
         <v>43336</v>
       </c>
-      <c r="B402">
+      <c r="B406">
         <v>1544.84</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A403" s="1">
+    <row r="407" spans="1:2">
+      <c r="A407" s="1">
         <v>43329</v>
       </c>
-      <c r="B403">
+      <c r="B407">
         <v>1514.74</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A404" s="1">
+    <row r="408" spans="1:2">
+      <c r="A408" s="1">
         <v>43322</v>
       </c>
-      <c r="B404">
+      <c r="B408">
         <v>1427.9</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A405" s="1">
+    <row r="409" spans="1:2">
+      <c r="A409" s="1">
         <v>43315</v>
       </c>
-      <c r="B405">
+      <c r="B409">
         <v>1380.62</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A406" s="1">
+    <row r="410" spans="1:2">
+      <c r="A410" s="1">
         <v>43308</v>
       </c>
-      <c r="B406">
+      <c r="B410">
         <v>1382.42</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A407" s="1">
+    <row r="411" spans="1:2">
+      <c r="A411" s="1">
         <v>43301</v>
       </c>
-      <c r="B407">
+      <c r="B411">
         <v>1411.88</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A408" s="1">
+    <row r="412" spans="1:2">
+      <c r="A412" s="1">
         <v>43294</v>
       </c>
-      <c r="B408">
+      <c r="B412">
         <v>1409.11</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A409" s="1">
+    <row r="413" spans="1:2">
+      <c r="A413" s="1">
         <v>43287</v>
       </c>
-      <c r="B409">
+      <c r="B413">
         <v>1402.61</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A410" s="1">
+    <row r="414" spans="1:2">
+      <c r="A414" s="1">
         <v>43280</v>
       </c>
-      <c r="B410">
+      <c r="B414">
         <v>1414.1</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A411" s="1">
+    <row r="415" spans="1:2">
+      <c r="A415" s="1">
         <v>43273</v>
       </c>
-      <c r="B411">
+      <c r="B415">
         <v>1399.79</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A412" s="1">
+    <row r="416" spans="1:2">
+      <c r="A416" s="1">
         <v>43266</v>
       </c>
-      <c r="B412">
+      <c r="B416">
         <v>1413.08</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A413" s="1">
+    <row r="417" spans="1:2">
+      <c r="A417" s="1">
         <v>43259</v>
       </c>
-      <c r="B413">
+      <c r="B417">
         <v>1417.1</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A414" s="1">
+    <row r="418" spans="1:2">
+      <c r="A418" s="1">
         <v>43252</v>
       </c>
-      <c r="B414">
+      <c r="B418">
         <v>1422.43</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A415" s="1">
+    <row r="419" spans="1:2">
+      <c r="A419" s="1">
         <v>43245</v>
       </c>
-      <c r="B415">
+      <c r="B419">
         <v>1406.43</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A416" s="1">
+    <row r="420" spans="1:2">
+      <c r="A420" s="1">
         <v>43238</v>
       </c>
-      <c r="B416">
+      <c r="B420">
         <v>1377.11</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A417" s="1">
+    <row r="421" spans="1:2">
+      <c r="A421" s="1">
         <v>43231</v>
       </c>
-      <c r="B417">
+      <c r="B421">
         <v>1354.97</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A418" s="1">
+    <row r="422" spans="1:2">
+      <c r="A422" s="1">
         <v>43224</v>
       </c>
-      <c r="B418">
+      <c r="B422">
         <v>1382.03</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A419" s="1">
+    <row r="423" spans="1:2">
+      <c r="A423" s="1">
         <v>43217</v>
       </c>
-      <c r="B419">
+      <c r="B423">
         <v>1413.58</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A420" s="1">
+    <row r="424" spans="1:2">
+      <c r="A424" s="1">
         <v>43210</v>
       </c>
-      <c r="B420">
+      <c r="B424">
         <v>1420.69</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A421" s="1">
+    <row r="425" spans="1:2">
+      <c r="A425" s="1">
         <v>43203</v>
       </c>
-      <c r="B421">
+      <c r="B425">
         <v>1424.04</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A422" s="1">
+    <row r="426" spans="1:2">
+      <c r="A426" s="1">
         <v>43196</v>
       </c>
-      <c r="B422">
+      <c r="B426">
         <v>1435.02</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A423" s="1">
+    <row r="427" spans="1:2">
+      <c r="A427" s="1">
         <v>43189</v>
       </c>
-      <c r="B423">
+      <c r="B427">
         <v>1443.3</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A424" s="1">
+    <row r="428" spans="1:2">
+      <c r="A428" s="1">
         <v>43182</v>
       </c>
-      <c r="B424">
+      <c r="B428">
         <v>1434.39</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A425" s="1">
+    <row r="429" spans="1:2">
+      <c r="A429" s="1">
         <v>43175</v>
       </c>
-      <c r="B425">
+      <c r="B429">
         <v>1434.13</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A426" s="1">
+    <row r="430" spans="1:2">
+      <c r="A430" s="1">
         <v>43168</v>
       </c>
-      <c r="B426">
+      <c r="B430">
         <v>1492.29</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A427" s="1">
+    <row r="431" spans="1:2">
+      <c r="A431" s="1">
         <v>43161</v>
       </c>
-      <c r="B427">
+      <c r="B431">
         <v>1505.62</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A428" s="1">
+    <row r="432" spans="1:2">
+      <c r="A432" s="1">
         <v>43154</v>
       </c>
-      <c r="B428">
+      <c r="B432">
         <v>1470.16</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A429" s="1">
+    <row r="433" spans="1:2">
+      <c r="A433" s="1">
         <v>43147</v>
       </c>
-      <c r="B429">
+      <c r="B433">
         <v>1426.16</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A430" s="1">
+    <row r="434" spans="1:2">
+      <c r="A434" s="1">
         <v>43140</v>
       </c>
-      <c r="B430">
+      <c r="B434">
         <v>1379.2</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A431" s="1">
+    <row r="435" spans="1:2">
+      <c r="A435" s="1">
         <v>43133</v>
       </c>
-      <c r="B431">
+      <c r="B435">
         <v>1306.54</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A432" s="1">
+    <row r="436" spans="1:2">
+      <c r="A436" s="1">
         <v>43126</v>
       </c>
-      <c r="B432">
+      <c r="B436">
         <v>1283.82</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A433" s="1">
+    <row r="437" spans="1:2">
+      <c r="A437" s="1">
         <v>43119</v>
       </c>
-      <c r="B433">
+      <c r="B437">
         <v>1294.79</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A434" s="1">
+    <row r="438" spans="1:2">
+      <c r="A438" s="1">
         <v>43112</v>
       </c>
-      <c r="B434">
+      <c r="B438">
         <v>1342.39</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A435" s="1">
+    <row r="439" spans="1:2">
+      <c r="A439" s="1">
         <v>43105</v>
       </c>
-      <c r="B435">
+      <c r="B439">
         <v>1365.95</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A436" s="1">
+    <row r="440" spans="1:2">
+      <c r="A440" s="1">
         <v>43098</v>
       </c>
-      <c r="B436">
+      <c r="B440">
         <v>1390.58</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A437" s="1">
+    <row r="441" spans="1:2">
+      <c r="A441" s="1">
         <v>43091</v>
       </c>
-      <c r="B437">
+      <c r="B441">
         <v>1416.05</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A438" s="1">
+    <row r="442" spans="1:2">
+      <c r="A442" s="1">
         <v>43084</v>
       </c>
-      <c r="B438">
+      <c r="B442">
         <v>1444.15</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A439" s="1">
+    <row r="443" spans="1:2">
+      <c r="A443" s="1">
         <v>43077</v>
       </c>
-      <c r="B439">
+      <c r="B443">
         <v>1459.76</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A440" s="1">
+    <row r="444" spans="1:2">
+      <c r="A444" s="1">
         <v>43070</v>
       </c>
-      <c r="B440">
+      <c r="B444">
         <v>1473.39</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A441" s="1">
+    <row r="445" spans="1:2">
+      <c r="A445" s="1">
         <v>43063</v>
       </c>
-      <c r="B441">
+      <c r="B445">
         <v>1449.46</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A442" s="1">
+    <row r="446" spans="1:2">
+      <c r="A446" s="1">
         <v>43056</v>
       </c>
-      <c r="B442">
+      <c r="B446">
         <v>1452.03</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A443" s="1">
+    <row r="447" spans="1:2">
+      <c r="A447" s="1">
         <v>43049</v>
       </c>
-      <c r="B443">
+      <c r="B447">
         <v>1414.46</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A444" s="1">
+    <row r="448" spans="1:2">
+      <c r="A448" s="1">
         <v>43042</v>
       </c>
-      <c r="B444">
+      <c r="B448">
         <v>1416.8</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A445" s="1">
+    <row r="449" spans="1:2">
+      <c r="A449" s="1">
         <v>43035</v>
       </c>
-      <c r="B445">
+      <c r="B449">
         <v>1438.57</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A446" s="1">
+    <row r="450" spans="1:2">
+      <c r="A450" s="1">
         <v>43028</v>
       </c>
-      <c r="B446">
+      <c r="B450">
         <v>1455.59</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A447" s="1">
+    <row r="451" spans="1:2">
+      <c r="A451" s="1">
         <v>43021</v>
       </c>
-      <c r="B447">
+      <c r="B451">
         <v>1442.27</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A448" s="1">
+    <row r="452" spans="1:2">
+      <c r="A452" s="1">
         <v>43014</v>
       </c>
-      <c r="B448">
+      <c r="B452">
         <v>1459.85</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A449" s="1">
+    <row r="453" spans="1:2">
+      <c r="A453" s="1">
         <v>43007</v>
       </c>
-      <c r="B449">
+      <c r="B453">
         <v>1506.85</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A450" s="1">
+    <row r="454" spans="1:2">
+      <c r="A454" s="1">
         <v>43000</v>
       </c>
-      <c r="B450">
+      <c r="B454">
         <v>1532.25</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A451" s="1">
+    <row r="455" spans="1:2">
+      <c r="A455" s="1">
         <v>42993</v>
       </c>
-      <c r="B451">
+      <c r="B455">
         <v>1597.79</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A452" s="1">
+    <row r="456" spans="1:2">
+      <c r="A456" s="1">
         <v>42986</v>
       </c>
-      <c r="B452">
+      <c r="B456">
         <v>1624.92</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A453" s="1">
+    <row r="457" spans="1:2">
+      <c r="A457" s="1">
         <v>42979</v>
       </c>
-      <c r="B453">
+      <c r="B457">
         <v>1615.17</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A454" s="1">
+    <row r="458" spans="1:2">
+      <c r="A458" s="1">
         <v>42972</v>
       </c>
-      <c r="B454">
+      <c r="B458">
         <v>1611.72</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A455" s="1">
+    <row r="459" spans="1:2">
+      <c r="A459" s="1">
         <v>42965</v>
       </c>
-      <c r="B455">
+      <c r="B459">
         <v>1625.92</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A456" s="1">
+    <row r="460" spans="1:2">
+      <c r="A460" s="1">
         <v>42958</v>
       </c>
-      <c r="B456">
+      <c r="B460">
         <v>1641.24</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A457" s="1">
+    <row r="461" spans="1:2">
+      <c r="A461" s="1">
         <v>42951</v>
       </c>
-      <c r="B457">
+      <c r="B461">
         <v>1632.76</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A458" s="1">
+    <row r="462" spans="1:2">
+      <c r="A462" s="1">
         <v>42944</v>
       </c>
-      <c r="B458">
+      <c r="B462">
         <v>1617.29</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A459" s="1">
+    <row r="463" spans="1:2">
+      <c r="A463" s="1">
         <v>42937</v>
       </c>
-      <c r="B459">
+      <c r="B463">
         <v>1625.7</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A460" s="1">
+    <row r="464" spans="1:2">
+      <c r="A464" s="1">
         <v>42930</v>
       </c>
-      <c r="B460">
+      <c r="B464">
         <v>1666.8</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A461" s="1">
+    <row r="465" spans="1:2">
+      <c r="A465" s="1">
         <v>42923</v>
       </c>
-      <c r="B461">
+      <c r="B465">
         <v>1748.41</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A462" s="1">
+    <row r="466" spans="1:2">
+      <c r="A466" s="1">
         <v>42916</v>
       </c>
-      <c r="B462">
+      <c r="B466">
         <v>1778.09</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A463" s="1">
+    <row r="467" spans="1:2">
+      <c r="A467" s="1">
         <v>42909</v>
       </c>
-      <c r="B463">
+      <c r="B467">
         <v>1755.81</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A464" s="1">
+    <row r="468" spans="1:2">
+      <c r="A468" s="1">
         <v>42902</v>
       </c>
-      <c r="B464">
+      <c r="B468">
         <v>1755.81</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A465" s="1">
+    <row r="469" spans="1:2">
+      <c r="A469" s="1">
         <v>42895</v>
       </c>
-      <c r="B465">
+      <c r="B469">
         <v>1765.98</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A466" s="1">
+    <row r="470" spans="1:2">
+      <c r="A470" s="1">
         <v>42888</v>
       </c>
-      <c r="B466">
+      <c r="B470">
         <v>1761.08</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A467" s="1">
+    <row r="471" spans="1:2">
+      <c r="A471" s="1">
         <v>42881</v>
       </c>
-      <c r="B467">
+      <c r="B471">
         <v>1734.8</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A468" s="1">
+    <row r="472" spans="1:2">
+      <c r="A472" s="1">
         <v>42874</v>
       </c>
-      <c r="B468">
+      <c r="B472">
         <v>1715.42</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A469" s="1">
+    <row r="473" spans="1:2">
+      <c r="A473" s="1">
         <v>42867</v>
       </c>
-      <c r="B469">
+      <c r="B473">
         <v>1696.48</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A470" s="1">
+    <row r="474" spans="1:2">
+      <c r="A474" s="1">
         <v>42860</v>
       </c>
-      <c r="B470">
+      <c r="B474">
         <v>1710.79</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A471" s="1">
+    <row r="475" spans="1:2">
+      <c r="A475" s="1">
         <v>42853</v>
       </c>
-      <c r="B471">
+      <c r="B475">
         <v>1674.22</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A472" s="1">
+    <row r="476" spans="1:2">
+      <c r="A476" s="1">
         <v>42846</v>
       </c>
-      <c r="B472">
+      <c r="B476">
         <v>1649.86</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A473" s="1">
+    <row r="477" spans="1:2">
+      <c r="A477" s="1">
         <v>42839</v>
       </c>
-      <c r="B473">
+      <c r="B477">
         <v>1618.59</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A474" s="1">
+    <row r="478" spans="1:2">
+      <c r="A478" s="1">
         <v>42832</v>
       </c>
-      <c r="B474">
+      <c r="B478">
         <v>1603.81</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A475" s="1">
+    <row r="479" spans="1:2">
+      <c r="A479" s="1">
         <v>42825</v>
       </c>
-      <c r="B475">
+      <c r="B479">
         <v>1551.23</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A476" s="1">
+    <row r="480" spans="1:2">
+      <c r="A480" s="1">
         <v>42818</v>
       </c>
-      <c r="B476">
+      <c r="B480">
         <v>1500.21</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A477" s="1">
+    <row r="481" spans="1:2">
+      <c r="A481" s="1">
         <v>42811</v>
       </c>
-      <c r="B477">
+      <c r="B481">
         <v>1463.54</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A478" s="1">
+    <row r="482" spans="1:2">
+      <c r="A482" s="1">
         <v>42804</v>
       </c>
-      <c r="B478">
+      <c r="B482">
         <v>1463.22</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A479" s="1">
+    <row r="483" spans="1:2">
+      <c r="A483" s="1">
         <v>42797</v>
       </c>
-      <c r="B479">
+      <c r="B483">
         <v>1406.1</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A480" s="1">
+    <row r="484" spans="1:2">
+      <c r="A484" s="1">
         <v>42790</v>
       </c>
-      <c r="B480">
+      <c r="B484">
         <v>1382.38</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A481" s="1">
+    <row r="485" spans="1:2">
+      <c r="A485" s="1">
         <v>42783</v>
       </c>
-      <c r="B481">
+      <c r="B485">
         <v>1382.29</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A482" s="1">
+    <row r="486" spans="1:2">
+      <c r="A486" s="1">
         <v>42776</v>
       </c>
-      <c r="B482">
+      <c r="B486">
         <v>1392.99</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A483" s="1">
+    <row r="487" spans="1:2">
+      <c r="A487" s="1">
         <v>42769</v>
       </c>
-      <c r="B483">
+      <c r="B487">
         <v>1394.48</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A484" s="1">
+    <row r="488" spans="1:2">
+      <c r="A488" s="1">
         <v>42762</v>
       </c>
-      <c r="B484">
+      <c r="B488">
         <v>1403.44</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A485" s="1">
+    <row r="489" spans="1:2">
+      <c r="A489" s="1">
         <v>42755</v>
       </c>
-      <c r="B485">
+      <c r="B489">
         <v>1406.78</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A486" s="1">
+    <row r="490" spans="1:2">
+      <c r="A490" s="1">
         <v>42748</v>
       </c>
-      <c r="B486">
+      <c r="B490">
         <v>1431.67</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A487" s="1">
+    <row r="491" spans="1:2">
+      <c r="A491" s="1">
         <v>42741</v>
       </c>
-      <c r="B487">
+      <c r="B491">
         <v>1422.88</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A488" s="1">
+    <row r="492" spans="1:2">
+      <c r="A492" s="1">
         <v>42734</v>
       </c>
-      <c r="B488">
+      <c r="B492">
         <v>1398.93</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A489" s="1">
+    <row r="493" spans="1:2">
+      <c r="A493" s="1">
         <v>42727</v>
       </c>
-      <c r="B489">
+      <c r="B493">
         <v>1422.68</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A490" s="1">
+    <row r="494" spans="1:2">
+      <c r="A494" s="1">
         <v>42720</v>
       </c>
-      <c r="B490">
+      <c r="B494">
         <v>1474.73</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A491" s="1">
+    <row r="495" spans="1:2">
+      <c r="A495" s="1">
         <v>42713</v>
       </c>
-      <c r="B491">
+      <c r="B495">
         <v>1473.17</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A492" s="1">
+    <row r="496" spans="1:2">
+      <c r="A496" s="1">
         <v>42706</v>
       </c>
-      <c r="B492">
+      <c r="B496">
         <v>1449.14</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A493" s="1">
+    <row r="497" spans="1:2">
+      <c r="A497" s="1">
         <v>42699</v>
       </c>
-      <c r="B493">
+      <c r="B497">
         <v>1444.87</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A494" s="1">
+    <row r="498" spans="1:2">
+      <c r="A498" s="1">
         <v>42692</v>
       </c>
-      <c r="B494">
+      <c r="B498">
         <v>1428.9</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A495" s="1">
+    <row r="499" spans="1:2">
+      <c r="A499" s="1">
         <v>42685</v>
       </c>
-      <c r="B495">
+      <c r="B499">
         <v>1424.91</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A496" s="1">
+    <row r="500" spans="1:2">
+      <c r="A500" s="1">
         <v>42678</v>
       </c>
-      <c r="B496">
+      <c r="B500">
         <v>1415.69</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A497" s="1">
+    <row r="501" spans="1:2">
+      <c r="A501" s="1">
         <v>42671</v>
       </c>
-      <c r="B497">
+      <c r="B501">
         <v>1405.31</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A498" s="1">
+    <row r="502" spans="1:2">
+      <c r="A502" s="1">
         <v>42664</v>
       </c>
-      <c r="B498">
+      <c r="B502">
         <v>1415.19</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A499" s="1">
+    <row r="503" spans="1:2">
+      <c r="A503" s="1">
         <v>42657</v>
       </c>
-      <c r="B499">
+      <c r="B503">
         <v>1464.98</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A500" s="1">
+    <row r="504" spans="1:2">
+      <c r="A504" s="1">
         <v>42650</v>
       </c>
-      <c r="B500">
+      <c r="B504">
         <v>1514.26</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A501" s="1">
+    <row r="505" spans="1:2">
+      <c r="A505" s="1">
         <v>42643</v>
       </c>
-      <c r="B501">
+      <c r="B505">
         <v>1550.89</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A502" s="1">
+    <row r="506" spans="1:2">
+      <c r="A506" s="1">
         <v>42636</v>
       </c>
-      <c r="B502">
+      <c r="B506">
         <v>1603.1</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A503" s="1">
+    <row r="507" spans="1:2">
+      <c r="A507" s="1">
         <v>42629</v>
       </c>
-      <c r="B503">
+      <c r="B507">
         <v>1609.33</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A504" s="1">
+    <row r="508" spans="1:2">
+      <c r="A508" s="1">
         <v>42622</v>
       </c>
-      <c r="B504">
+      <c r="B508">
         <v>1578.87</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A505" s="1">
+    <row r="509" spans="1:2">
+      <c r="A509" s="1">
         <v>42615</v>
       </c>
-      <c r="B505">
+      <c r="B509">
         <v>1576.82</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A506" s="1">
+    <row r="510" spans="1:2">
+      <c r="A510" s="1">
         <v>42608</v>
       </c>
-      <c r="B506">
+      <c r="B510">
         <v>1572.58</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A507" s="1">
+    <row r="511" spans="1:2">
+      <c r="A511" s="1">
         <v>42601</v>
       </c>
-      <c r="B507">
+      <c r="B511">
         <v>1580.54</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A508" s="1">
+    <row r="512" spans="1:2">
+      <c r="A512" s="1">
         <v>42594</v>
       </c>
-      <c r="B508">
+      <c r="B512">
         <v>1554.91</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A509" s="1">
+    <row r="513" spans="1:2">
+      <c r="A513" s="1">
         <v>42587</v>
       </c>
-      <c r="B509">
+      <c r="B513">
         <v>1601.8</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A510" s="1">
+    <row r="514" spans="1:2">
+      <c r="A514" s="1">
         <v>42580</v>
       </c>
-      <c r="B510">
+      <c r="B514">
         <v>1602.36</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A511" s="1">
+    <row r="515" spans="1:2">
+      <c r="A515" s="1">
         <v>42573</v>
       </c>
-      <c r="B511">
+      <c r="B515">
         <v>1590.41</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A512" s="1">
+    <row r="516" spans="1:2">
+      <c r="A516" s="1">
         <v>42566</v>
       </c>
-      <c r="B512">
+      <c r="B516">
         <v>1572.8</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A513" s="1">
+    <row r="517" spans="1:2">
+      <c r="A517" s="1">
         <v>42559</v>
       </c>
-      <c r="B513">
+      <c r="B517">
         <v>1585.94</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A514" s="1">
+    <row r="518" spans="1:2">
+      <c r="A518" s="1">
         <v>42552</v>
       </c>
-      <c r="B514">
+      <c r="B518">
         <v>1532</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A515" s="1">
+    <row r="519" spans="1:2">
+      <c r="A519" s="1">
         <v>42545</v>
       </c>
-      <c r="B515">
+      <c r="B519">
         <v>1521.5</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A516" s="1">
+    <row r="520" spans="1:2">
+      <c r="A520" s="1">
         <v>42538</v>
       </c>
-      <c r="B516">
+      <c r="B520">
         <v>1485.63</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A517" s="1">
+    <row r="521" spans="1:2">
+      <c r="A521" s="1">
         <v>42531</v>
       </c>
-      <c r="B517">
+      <c r="B521">
         <v>1433.12</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A518" s="1">
+    <row r="522" spans="1:2">
+      <c r="A522" s="1">
         <v>42524</v>
       </c>
-      <c r="B518">
+      <c r="B522">
         <v>1417.53</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A519" s="1">
+    <row r="523" spans="1:2">
+      <c r="A523" s="1">
         <v>42517</v>
       </c>
-      <c r="B519">
+      <c r="B523">
         <v>1373.37</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A520" s="1">
+    <row r="524" spans="1:2">
+      <c r="A524" s="1">
         <v>42510</v>
       </c>
-      <c r="B520">
+      <c r="B524">
         <v>1356.05</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A521" s="1">
+    <row r="525" spans="1:2">
+      <c r="A525" s="1">
         <v>42503</v>
       </c>
-      <c r="B521">
+      <c r="B525">
         <v>1331.18</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A522" s="1">
+    <row r="526" spans="1:2">
+      <c r="A526" s="1">
         <v>42496</v>
       </c>
-      <c r="B522">
+      <c r="B526">
         <v>1287.3499999999999</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A523" s="1">
+    <row r="527" spans="1:2">
+      <c r="A527" s="1">
         <v>42489</v>
       </c>
-      <c r="B523">
+      <c r="B527">
         <v>1234.33</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A524" s="1">
+    <row r="528" spans="1:2">
+      <c r="A528" s="1">
         <v>42482</v>
       </c>
-      <c r="B524">
+      <c r="B528">
         <v>1214.74</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A525" s="1">
+    <row r="529" spans="1:2">
+      <c r="A529" s="1">
         <v>42475</v>
       </c>
-      <c r="B525">
+      <c r="B529">
         <v>1218.68</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A526" s="1">
+    <row r="530" spans="1:2">
+      <c r="A530" s="1">
         <v>42468</v>
       </c>
-      <c r="B526">
+      <c r="B530">
         <v>1231.47</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A527" s="1">
+    <row r="531" spans="1:2">
+      <c r="A531" s="1">
         <v>42461</v>
       </c>
-      <c r="B527">
+      <c r="B531">
         <v>1255.8800000000001</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A528" s="1">
+    <row r="532" spans="1:2">
+      <c r="A532" s="1">
         <v>42454</v>
       </c>
-      <c r="B528">
+      <c r="B532">
         <v>1281.51</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A529" s="1">
+    <row r="533" spans="1:2">
+      <c r="A533" s="1">
         <v>42447</v>
       </c>
-      <c r="B529">
+      <c r="B533">
         <v>1266.1099999999999</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A530" s="1">
+    <row r="534" spans="1:2">
+      <c r="A534" s="1">
         <v>42440</v>
       </c>
-      <c r="B530">
+      <c r="B534">
         <v>1219.43</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A531" s="1">
+    <row r="535" spans="1:2">
+      <c r="A535" s="1">
         <v>42433</v>
       </c>
-      <c r="B531">
+      <c r="B535">
         <v>1191.8900000000001</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A532" s="1">
+    <row r="536" spans="1:2">
+      <c r="A536" s="1">
         <v>42426</v>
       </c>
-      <c r="B532">
+      <c r="B536">
         <v>1231.54</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A533" s="1">
+    <row r="537" spans="1:2">
+      <c r="A537" s="1">
         <v>42419</v>
       </c>
-      <c r="B533">
+      <c r="B537">
         <v>1275.47</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A534" s="1">
+    <row r="538" spans="1:2">
+      <c r="A538" s="1">
         <v>42412</v>
       </c>
-      <c r="B534">
+      <c r="B538">
         <v>1302.1199999999999</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A535" s="1">
+    <row r="539" spans="1:2">
+      <c r="A539" s="1">
         <v>42405</v>
       </c>
-      <c r="B535">
+      <c r="B539">
         <v>1293.6600000000001</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A536" s="1">
+    <row r="540" spans="1:2">
+      <c r="A540" s="1">
         <v>42398</v>
       </c>
-      <c r="B536">
+      <c r="B540">
         <v>1273.43</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A537" s="1">
+    <row r="541" spans="1:2">
+      <c r="A541" s="1">
         <v>42391</v>
       </c>
-      <c r="B537">
+      <c r="B541">
         <v>1277.3699999999999</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A538" s="1">
+    <row r="542" spans="1:2">
+      <c r="A542" s="1">
         <v>42384</v>
       </c>
-      <c r="B538">
+      <c r="B542">
         <v>1287.72</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A539" s="1">
+    <row r="543" spans="1:2">
+      <c r="A543" s="1">
         <v>42377</v>
       </c>
-      <c r="B539">
+      <c r="B543">
         <v>1261.3699999999999</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A540" s="1">
+    <row r="544" spans="1:2">
+      <c r="A544" s="1">
         <v>42370</v>
       </c>
-      <c r="B540">
+      <c r="B544">
         <v>1237.31</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A541" s="1">
+    <row r="545" spans="1:2">
+      <c r="A545" s="1">
         <v>42363</v>
       </c>
-      <c r="B541">
+      <c r="B545">
         <v>1233.43</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A542" s="1">
+    <row r="546" spans="1:2">
+      <c r="A546" s="1">
         <v>42356</v>
       </c>
-      <c r="B542">
+      <c r="B546">
         <v>1223.3399999999999</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A543" s="1">
+    <row r="547" spans="1:2">
+      <c r="A547" s="1">
         <v>42349</v>
       </c>
-      <c r="B543">
+      <c r="B547">
         <v>1231.8399999999999</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A544" s="1">
+    <row r="548" spans="1:2">
+      <c r="A548" s="1">
         <v>42342</v>
       </c>
-      <c r="B544">
+      <c r="B548">
         <v>1190.06</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A545" s="1">
+    <row r="549" spans="1:2">
+      <c r="A549" s="1">
         <v>42335</v>
       </c>
-      <c r="B545">
+      <c r="B549">
         <v>1187.5899999999999</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A546" s="1">
+    <row r="550" spans="1:2">
+      <c r="A550" s="1">
         <v>42328</v>
       </c>
-      <c r="B546">
+      <c r="B550">
         <v>1212.1199999999999</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A547" s="1">
+    <row r="551" spans="1:2">
+      <c r="A551" s="1">
         <v>42321</v>
       </c>
-      <c r="B547">
+      <c r="B551">
         <v>1264.83</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A548" s="1">
+    <row r="552" spans="1:2">
+      <c r="A552" s="1">
         <v>42314</v>
       </c>
-      <c r="B548">
+      <c r="B552">
         <v>1295.08</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A549" s="1">
+    <row r="553" spans="1:2">
+      <c r="A553" s="1">
         <v>42307</v>
       </c>
-      <c r="B549">
+      <c r="B553">
         <v>1347.53</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A550" s="1">
+    <row r="554" spans="1:2">
+      <c r="A554" s="1">
         <v>42300</v>
       </c>
-      <c r="B550">
+      <c r="B554">
         <v>1347.69</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A551" s="1">
+    <row r="555" spans="1:2">
+      <c r="A555" s="1">
         <v>42293</v>
       </c>
-      <c r="B551">
+      <c r="B555">
         <v>1344.79</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A552" s="1">
+    <row r="556" spans="1:2">
+      <c r="A556" s="1">
         <v>42286</v>
       </c>
-      <c r="B552">
+      <c r="B556">
         <v>1341.34</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A553" s="1">
+    <row r="557" spans="1:2">
+      <c r="A557" s="1">
         <v>42279</v>
       </c>
-      <c r="B553">
+      <c r="B557">
         <v>1372.61</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A554" s="1">
+    <row r="558" spans="1:2">
+      <c r="A558" s="1">
         <v>42272</v>
       </c>
-      <c r="B554">
+      <c r="B558">
         <v>1421.95</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A555" s="1">
+    <row r="559" spans="1:2">
+      <c r="A559" s="1">
         <v>42265</v>
       </c>
-      <c r="B555">
+      <c r="B559">
         <v>1404.1</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A556" s="1">
+    <row r="560" spans="1:2">
+      <c r="A560" s="1">
         <v>42258</v>
       </c>
-      <c r="B556">
+      <c r="B560">
         <v>1389.3</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A557" s="1">
+    <row r="561" spans="1:2">
+      <c r="A561" s="1">
         <v>42251</v>
       </c>
-      <c r="B557">
+      <c r="B561">
         <v>1349.49</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A558" s="1">
+    <row r="562" spans="1:2">
+      <c r="A562" s="1">
         <v>42244</v>
       </c>
-      <c r="B558">
+      <c r="B562">
         <v>1310.26</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A559" s="1">
+    <row r="563" spans="1:2">
+      <c r="A563" s="1">
         <v>42237</v>
       </c>
-      <c r="B559">
+      <c r="B563">
         <v>1303.1500000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A560" s="1">
+    <row r="564" spans="1:2">
+      <c r="A564" s="1">
         <v>42230</v>
       </c>
-      <c r="B560">
+      <c r="B564">
         <v>1281.3499999999999</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A561" s="1">
+    <row r="565" spans="1:2">
+      <c r="A565" s="1">
         <v>42223</v>
       </c>
-      <c r="B561">
+      <c r="B565">
         <v>1287.8399999999999</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A562" s="1">
+    <row r="566" spans="1:2">
+      <c r="A566" s="1">
         <v>42216</v>
       </c>
-      <c r="B562">
+      <c r="B566">
         <v>1291.02</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A563" s="1">
+    <row r="567" spans="1:2">
+      <c r="A567" s="1">
         <v>42209</v>
       </c>
-      <c r="B563">
+      <c r="B567">
         <v>1292.98</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A564" s="1">
+    <row r="568" spans="1:2">
+      <c r="A568" s="1">
         <v>42202</v>
       </c>
-      <c r="B564">
+      <c r="B568">
         <v>1279.94</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A565" s="1">
+    <row r="569" spans="1:2">
+      <c r="A569" s="1">
         <v>42195</v>
       </c>
-      <c r="B565">
+      <c r="B569">
         <v>1289.6099999999999</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A566" s="1">
+    <row r="570" spans="1:2">
+      <c r="A570" s="1">
         <v>42188</v>
       </c>
-      <c r="B566">
+      <c r="B570">
         <v>1278.98</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A567" s="1">
+    <row r="571" spans="1:2">
+      <c r="A571" s="1">
         <v>42181</v>
       </c>
-      <c r="B567">
+      <c r="B571">
         <v>1289.22</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A568" s="1">
+    <row r="572" spans="1:2">
+      <c r="A572" s="1">
         <v>42174</v>
       </c>
-      <c r="B568">
+      <c r="B572">
         <v>1354.74</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A569" s="1">
+    <row r="573" spans="1:2">
+      <c r="A573" s="1">
         <v>42167</v>
       </c>
-      <c r="B569">
+      <c r="B573">
         <v>1346.98</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A570" s="1">
+    <row r="574" spans="1:2">
+      <c r="A574" s="1">
         <v>42160</v>
       </c>
-      <c r="B570">
+      <c r="B574">
         <v>1331.62</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A571" s="1">
+    <row r="575" spans="1:2">
+      <c r="A575" s="1">
         <v>42153</v>
       </c>
-      <c r="B571">
+      <c r="B575">
         <v>1272.71</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A572" s="1">
+    <row r="576" spans="1:2">
+      <c r="A576" s="1">
         <v>42146</v>
       </c>
-      <c r="B572">
+      <c r="B576">
         <v>1238.01</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A573" s="1">
+    <row r="577" spans="1:2">
+      <c r="A577" s="1">
         <v>42139</v>
       </c>
-      <c r="B573">
+      <c r="B577">
         <v>1208.26</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A574" s="1">
+    <row r="578" spans="1:2">
+      <c r="A578" s="1">
         <v>42132</v>
       </c>
-      <c r="B574">
+      <c r="B578">
         <v>1207.23</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A575" s="1">
+    <row r="579" spans="1:2">
+      <c r="A579" s="1">
         <v>42125</v>
       </c>
-      <c r="B575">
+      <c r="B579">
         <v>1261.18</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A576" s="1">
+    <row r="580" spans="1:2">
+      <c r="A580" s="1">
         <v>42118</v>
       </c>
-      <c r="B576">
+      <c r="B580">
         <v>1285.7</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A577" s="1">
+    <row r="581" spans="1:2">
+      <c r="A581" s="1">
         <v>42111</v>
       </c>
-      <c r="B577">
+      <c r="B581">
         <v>1280.32</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A578" s="1">
+    <row r="582" spans="1:2">
+      <c r="A582" s="1">
         <v>42104</v>
       </c>
-      <c r="B578">
+      <c r="B582">
         <v>1260.04</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A579" s="1">
+    <row r="583" spans="1:2">
+      <c r="A583" s="1">
         <v>42097</v>
       </c>
-      <c r="B579">
+      <c r="B583">
         <v>1254.81</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A580" s="1">
+    <row r="584" spans="1:2">
+      <c r="A584" s="1">
         <v>42090</v>
       </c>
-      <c r="B580">
+      <c r="B584">
         <v>1248.23</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A581" s="1">
+    <row r="585" spans="1:2">
+      <c r="A585" s="1">
         <v>42083</v>
       </c>
-      <c r="B581">
+      <c r="B585">
         <v>1253.75</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A582" s="1">
+    <row r="586" spans="1:2">
+      <c r="A586" s="1">
         <v>42076</v>
       </c>
-      <c r="B582">
+      <c r="B586">
         <v>1253.24</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A583" s="1">
+    <row r="587" spans="1:2">
+      <c r="A587" s="1">
         <v>42069</v>
       </c>
-      <c r="B583">
+      <c r="B587">
         <v>1276.71</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A584" s="1">
+    <row r="588" spans="1:2">
+      <c r="A588" s="1">
         <v>42062</v>
       </c>
-      <c r="B584">
+      <c r="B588">
         <v>1295.79</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A585" s="1">
+    <row r="589" spans="1:2">
+      <c r="A589" s="1">
         <v>42055</v>
       </c>
-      <c r="B585">
+      <c r="B589">
         <v>1264.2</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A586" s="1">
+    <row r="590" spans="1:2">
+      <c r="A590" s="1">
         <v>42048</v>
       </c>
-      <c r="B586">
+      <c r="B590">
         <v>1223.4100000000001</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A587" s="1">
+    <row r="591" spans="1:2">
+      <c r="A591" s="1">
         <v>42041</v>
       </c>
-      <c r="B587">
+      <c r="B591">
         <v>1181.5899999999999</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A588" s="1">
+    <row r="592" spans="1:2">
+      <c r="A592" s="1">
         <v>42034</v>
       </c>
-      <c r="B588">
+      <c r="B592">
         <v>1173.68</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A589" s="1">
+    <row r="593" spans="1:2">
+      <c r="A593" s="1">
         <v>42027</v>
       </c>
-      <c r="B589">
+      <c r="B593">
         <v>1150.98</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A590" s="1">
+    <row r="594" spans="1:2">
+      <c r="A594" s="1">
         <v>42020</v>
       </c>
-      <c r="B590">
+      <c r="B594">
         <v>1149.96</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A591" s="1">
+    <row r="595" spans="1:2">
+      <c r="A595" s="1">
         <v>42013</v>
       </c>
-      <c r="B591">
+      <c r="B595">
         <v>1193.9100000000001</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A592" s="1">
+    <row r="596" spans="1:2">
+      <c r="A596" s="1">
         <v>42006</v>
       </c>
-      <c r="B592">
+      <c r="B596">
         <v>1214.69</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A593" s="1">
+    <row r="597" spans="1:2">
+      <c r="A597" s="1">
         <v>41999</v>
       </c>
-      <c r="B593">
+      <c r="B597">
         <v>1227.5999999999999</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A594" s="1">
+    <row r="598" spans="1:2">
+      <c r="A598" s="1">
         <v>41992</v>
       </c>
-      <c r="B594">
+      <c r="B598">
         <v>1221.23</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A595" s="1">
+    <row r="599" spans="1:2">
+      <c r="A599" s="1">
         <v>41985</v>
       </c>
-      <c r="B595">
+      <c r="B599">
         <v>1243.25</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A596" s="1">
+    <row r="600" spans="1:2">
+      <c r="A600" s="1">
         <v>41978</v>
       </c>
-      <c r="B596">
+      <c r="B600">
         <v>1207.1199999999999</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A597" s="1">
+    <row r="601" spans="1:2">
+      <c r="A601" s="1">
         <v>41971</v>
       </c>
-      <c r="B597">
+      <c r="B601">
         <v>1231.94</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A598" s="1">
+    <row r="602" spans="1:2">
+      <c r="A602" s="1">
         <v>41964</v>
       </c>
-      <c r="B598">
+      <c r="B602">
         <v>1208.6199999999999</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A599" s="1">
+    <row r="603" spans="1:2">
+      <c r="A603" s="1">
         <v>41957</v>
       </c>
-      <c r="B599">
+      <c r="B603">
         <v>1216.45</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A600" s="1">
+    <row r="604" spans="1:2">
+      <c r="A604" s="1">
         <v>41950</v>
       </c>
-      <c r="B600">
+      <c r="B604">
         <v>1217.98</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A601" s="1">
+    <row r="605" spans="1:2">
+      <c r="A605" s="1">
         <v>41943</v>
       </c>
-      <c r="B601">
+      <c r="B605">
         <v>1217.42</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A602" s="1">
+    <row r="606" spans="1:2">
+      <c r="A606" s="1">
         <v>41936</v>
       </c>
-      <c r="B602">
+      <c r="B606">
         <v>1203.1099999999999</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A603" s="1">
+    <row r="607" spans="1:2">
+      <c r="A607" s="1">
         <v>41929</v>
       </c>
-      <c r="B603">
+      <c r="B607">
         <v>1198.22</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A604" s="1">
+    <row r="608" spans="1:2">
+      <c r="A608" s="1">
         <v>41922</v>
       </c>
-      <c r="B604">
+      <c r="B608">
         <v>1184.79</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A605" s="1">
+    <row r="609" spans="1:2">
+      <c r="A609" s="1">
         <v>41915</v>
       </c>
-      <c r="B605">
+      <c r="B609">
         <v>1203.52</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A606" s="1">
+    <row r="610" spans="1:2">
+      <c r="A610" s="1">
         <v>41908</v>
       </c>
-      <c r="B606">
+      <c r="B610">
         <v>1246.25</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A607" s="1">
+    <row r="611" spans="1:2">
+      <c r="A611" s="1">
         <v>41901</v>
       </c>
-      <c r="B607">
+      <c r="B611">
         <v>1299.48</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A608" s="1">
+    <row r="612" spans="1:2">
+      <c r="A612" s="1">
         <v>41894</v>
       </c>
-      <c r="B608">
+      <c r="B612">
         <v>1371.39</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A609" s="1">
+    <row r="613" spans="1:2">
+      <c r="A613" s="1">
         <v>41887</v>
       </c>
-      <c r="B609">
+      <c r="B613">
         <v>1373.74</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A610" s="1">
+    <row r="614" spans="1:2">
+      <c r="A614" s="1">
         <v>41880</v>
       </c>
-      <c r="B610">
+      <c r="B614">
         <v>1369.49</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A611" s="1">
+    <row r="615" spans="1:2">
+      <c r="A615" s="1">
         <v>41873</v>
       </c>
-      <c r="B611">
+      <c r="B615">
         <v>1364.54</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A612" s="1">
+    <row r="616" spans="1:2">
+      <c r="A616" s="1">
         <v>41866</v>
       </c>
-      <c r="B612">
+      <c r="B616">
         <v>1375.33</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A613" s="1">
+    <row r="617" spans="1:2">
+      <c r="A617" s="1">
         <v>41859</v>
       </c>
-      <c r="B613">
+      <c r="B617">
         <v>1393.34</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A614" s="1">
+    <row r="618" spans="1:2">
+      <c r="A618" s="1">
         <v>41852</v>
       </c>
-      <c r="B614">
+      <c r="B618">
         <v>1403.92</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A615" s="1">
+    <row r="619" spans="1:2">
+      <c r="A619" s="1">
         <v>41845</v>
       </c>
-      <c r="B615">
+      <c r="B619">
         <v>1382.26</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A616" s="1">
+    <row r="620" spans="1:2">
+      <c r="A620" s="1">
         <v>41838</v>
       </c>
-      <c r="B616">
+      <c r="B620">
         <v>1406.7</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A617" s="1">
+    <row r="621" spans="1:2">
+      <c r="A621" s="1">
         <v>41831</v>
       </c>
-      <c r="B617">
+      <c r="B621">
         <v>1470.14</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A618" s="1">
+    <row r="622" spans="1:2">
+      <c r="A622" s="1">
         <v>41824</v>
       </c>
-      <c r="B618">
+      <c r="B622">
         <v>1517.6</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A619" s="1">
+    <row r="623" spans="1:2">
+      <c r="A623" s="1">
         <v>41817</v>
       </c>
-      <c r="B619">
+      <c r="B623">
         <v>1512.95</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A620" s="1">
+    <row r="624" spans="1:2">
+      <c r="A624" s="1">
         <v>41810</v>
       </c>
-      <c r="B620">
+      <c r="B624">
         <v>1468.39</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A621" s="1">
+    <row r="625" spans="1:2">
+      <c r="A625" s="1">
         <v>41803</v>
       </c>
-      <c r="B621">
+      <c r="B625">
         <v>1422.55</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A622" s="1">
+    <row r="626" spans="1:2">
+      <c r="A626" s="1">
         <v>41796</v>
       </c>
-      <c r="B622">
+      <c r="B626">
         <v>1407.45</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A623" s="1">
+    <row r="627" spans="1:2">
+      <c r="A627" s="1">
         <v>41789</v>
       </c>
-      <c r="B623">
+      <c r="B627">
         <v>1402.16</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A624" s="1">
+    <row r="628" spans="1:2">
+      <c r="A628" s="1">
         <v>41782</v>
       </c>
-      <c r="B624">
+      <c r="B628">
         <v>1365.12</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A625" s="1">
+    <row r="629" spans="1:2">
+      <c r="A629" s="1">
         <v>41775</v>
       </c>
-      <c r="B625">
+      <c r="B629">
         <v>1334.78</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A626" s="1">
+    <row r="630" spans="1:2">
+      <c r="A630" s="1">
         <v>41768</v>
       </c>
-      <c r="B626">
+      <c r="B630">
         <v>1334.14</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A627" s="1">
+    <row r="631" spans="1:2">
+      <c r="A631" s="1">
         <v>41761</v>
       </c>
-      <c r="B627">
+      <c r="B631">
         <v>1351.29</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A628" s="1">
+    <row r="632" spans="1:2">
+      <c r="A632" s="1">
         <v>41754</v>
       </c>
-      <c r="B628">
+      <c r="B632">
         <v>1356.68</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A629" s="1">
+    <row r="633" spans="1:2">
+      <c r="A633" s="1">
         <v>41747</v>
       </c>
-      <c r="B629">
+      <c r="B633">
         <v>1354.64</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A630" s="1">
+    <row r="634" spans="1:2">
+      <c r="A634" s="1">
         <v>41740</v>
       </c>
-      <c r="B630">
+      <c r="B634">
         <v>1364.14</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A631" s="1">
+    <row r="635" spans="1:2">
+      <c r="A635" s="1">
         <v>41733</v>
       </c>
-      <c r="B631">
+      <c r="B635">
         <v>1328.84</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A632" s="1">
+    <row r="636" spans="1:2">
+      <c r="A636" s="1">
         <v>41726</v>
       </c>
-      <c r="B632">
+      <c r="B636">
         <v>1311.02</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A633" s="1">
+    <row r="637" spans="1:2">
+      <c r="A637" s="1">
         <v>41719</v>
       </c>
-      <c r="B633">
+      <c r="B637">
         <v>1344.11</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A634" s="1">
+    <row r="638" spans="1:2">
+      <c r="A638" s="1">
         <v>41712</v>
       </c>
-      <c r="B634">
+      <c r="B638">
         <v>1299.22</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A635" s="1">
+    <row r="639" spans="1:2">
+      <c r="A639" s="1">
         <v>41705</v>
       </c>
-      <c r="B635">
+      <c r="B639">
         <v>1241.7</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A636" s="1">
+    <row r="640" spans="1:2">
+      <c r="A640" s="1">
         <v>41698</v>
       </c>
-      <c r="B636">
+      <c r="B640">
         <v>1254.27</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A637" s="1">
+    <row r="641" spans="1:2">
+      <c r="A641" s="1">
         <v>41691</v>
       </c>
-      <c r="B637">
+      <c r="B641">
         <v>1281.67</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A638" s="1">
+    <row r="642" spans="1:2">
+      <c r="A642" s="1">
         <v>41684</v>
       </c>
-      <c r="B638">
+      <c r="B642">
         <v>1290.3499999999999</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A639" s="1">
+    <row r="643" spans="1:2">
+      <c r="A643" s="1">
         <v>41677</v>
       </c>
-      <c r="B639">
+      <c r="B643">
         <v>1328.73</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A640" s="1">
+    <row r="644" spans="1:2">
+      <c r="A644" s="1">
         <v>41670</v>
       </c>
-      <c r="B640">
+      <c r="B644">
         <v>1377.36</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A641" s="1">
+    <row r="645" spans="1:2">
+      <c r="A645" s="1">
         <v>41663</v>
       </c>
-      <c r="B641">
+      <c r="B645">
         <v>1348.11</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A642" s="1">
+    <row r="646" spans="1:2">
+      <c r="A646" s="1">
         <v>41656</v>
       </c>
-      <c r="B642">
+      <c r="B646">
         <v>1308.2</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A643" s="1">
+    <row r="647" spans="1:2">
+      <c r="A647" s="1">
         <v>41649</v>
       </c>
-      <c r="B643">
+      <c r="B647">
         <v>1306.05</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A644" s="1">
+    <row r="648" spans="1:2">
+      <c r="A648" s="1">
         <v>41642</v>
       </c>
-      <c r="B644">
+      <c r="B648">
         <v>1397.22</v>
       </c>
     </row>
